--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Đề tài - Bánh ăn dặm VIAM 2027" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Đề tài - Mẫu trắng dự án mới" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Bánh ăn dặm VIAM 2027" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Mẫu trắng dự án mới" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -56,6 +56,9 @@
       <color indexed="9"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -102,13 +105,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1988,7 +1992,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Lý lịch khoa học-TruongHongSon.doc</t>
+          <t>Lý lịch khoa học - Trương Hồng Sơn.docx</t>
         </is>
       </c>
       <c r="F67">

--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -715,92 +715,80 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Địa điểm triển khai nghiên cứu (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12">
+        <f>IF(ISBLANK(C12), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>SEC_B</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>PHẦN B: BAN CHỦ NHIỆM &amp; NGHIÊN CỨU VIÊN ĐỀ TÀI (TỐI ĐA 20 NGƯỜI)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Chủ nhiệm đề tài (CNĐT - Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Trương Hồng Sơn</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>TS.BS.</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Viện trưởng - Viện Y học Ứng dụng VN</t>
-        </is>
-      </c>
-      <c r="F13">
-        <f>IF(ISBLANK(C13), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Đồng Chủ nhiệm đề tài (Tùy chọn)</t>
+          <t>Chủ nhiệm đề tài (CNĐT - Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Trương Hồng Sơn</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>TS.BS.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Viện trưởng - Viện Y học Ứng dụng VN</t>
         </is>
       </c>
       <c r="F14">
-        <f>IF(ISBLANK(C14), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C14), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Thư ký Đề tài (Khác Thư ký HĐ - Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Lưu Liên Hương</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
+          <t>Đồng Chủ nhiệm đề tài (Tùy chọn)</t>
         </is>
       </c>
       <c r="F15">
@@ -811,17 +799,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 1</t>
+          <t>Thư ký Đề tài (Khác Thư ký HĐ - Tùy chọn)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lê Việt Anh</t>
+          <t>Lưu Liên Hương</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -842,27 +830,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 2</t>
+          <t>Nghiên cứu viên 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lê Minh Khánh</t>
+          <t>Lê Việt Anh</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bác sĩ</t>
+          <t>Thạc sĩ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Phòng khám VIAM</t>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
       <c r="F17">
@@ -873,12 +861,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B06</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 3</t>
+          <t>Nghiên cứu viên 2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Lê Minh Khánh</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bác sĩ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Phòng khám VIAM</t>
         </is>
       </c>
       <c r="F18">
@@ -889,12 +892,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B07</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 4</t>
+          <t>Nghiên cứu viên 3</t>
         </is>
       </c>
       <c r="F19">
@@ -905,12 +908,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B08</t>
+          <t>B07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 5</t>
+          <t>Nghiên cứu viên 4</t>
         </is>
       </c>
       <c r="F20">
@@ -921,12 +924,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B09</t>
+          <t>B08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 6</t>
+          <t>Nghiên cứu viên 5</t>
         </is>
       </c>
       <c r="F21">
@@ -937,12 +940,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B10</t>
+          <t>B09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 7</t>
+          <t>Nghiên cứu viên 6</t>
         </is>
       </c>
       <c r="F22">
@@ -953,12 +956,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>B10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 8</t>
+          <t>Nghiên cứu viên 7</t>
         </is>
       </c>
       <c r="F23">
@@ -969,12 +972,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 9</t>
+          <t>Nghiên cứu viên 8</t>
         </is>
       </c>
       <c r="F24">
@@ -985,12 +988,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B13</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 10</t>
+          <t>Nghiên cứu viên 9</t>
         </is>
       </c>
       <c r="F25">
@@ -1001,12 +1004,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>B13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 11</t>
+          <t>Nghiên cứu viên 10</t>
         </is>
       </c>
       <c r="F26">
@@ -1017,12 +1020,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B15</t>
+          <t>B14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 12</t>
+          <t>Nghiên cứu viên 11</t>
         </is>
       </c>
       <c r="F27">
@@ -1033,12 +1036,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B16</t>
+          <t>B15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 13</t>
+          <t>Nghiên cứu viên 12</t>
         </is>
       </c>
       <c r="F28">
@@ -1049,12 +1052,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B17</t>
+          <t>B16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 14</t>
+          <t>Nghiên cứu viên 13</t>
         </is>
       </c>
       <c r="F29">
@@ -1065,12 +1068,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B18</t>
+          <t>B17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 15</t>
+          <t>Nghiên cứu viên 14</t>
         </is>
       </c>
       <c r="F30">
@@ -1081,12 +1084,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B19</t>
+          <t>B18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 16</t>
+          <t>Nghiên cứu viên 15</t>
         </is>
       </c>
       <c r="F31">
@@ -1097,12 +1100,12 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B20</t>
+          <t>B19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 17</t>
+          <t>Nghiên cứu viên 16</t>
         </is>
       </c>
       <c r="F32">
@@ -1111,76 +1114,61 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nghiên cứu viên 17</t>
+        </is>
+      </c>
+      <c r="F33">
+        <f>IF(ISBLANK(C33), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>SEC_C</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>PHẦN C: HỘI ĐỒNG ĐẠO ĐỨC TRONG NGHIÊN CỨU (HĐ 01 - 7 THÀNH VIÊN BẮT BUỘC)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Chủ tịch HĐ Đạo đức (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Nguyễn Công Khẩn</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>GS.TS.</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
-        </is>
-      </c>
-      <c r="F34">
-        <f>IF(ISBLANK(C34), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Chủ tịch HĐ Đạo đức (Bắt buộc)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Xuân Ninh</t>
+          <t>Nguyễn Công Khẩn</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>GS.TS.</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
         </is>
       </c>
       <c r="F35">
@@ -1191,17 +1179,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Lê Bạch Mai</t>
+          <t>Nguyễn Xuân Ninh</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -1211,7 +1199,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
         </is>
       </c>
       <c r="F36">
@@ -1222,17 +1210,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Lâm</t>
+          <t>Lê Bạch Mai</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1253,17 +1241,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Đạo đức 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Quang Dũng</t>
+          <t>Nguyễn Thị Lâm</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -1273,7 +1261,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Bộ môn Dinh dưỡng - ĐH Y Hà Nội</t>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
         </is>
       </c>
       <c r="F38">
@@ -1284,28 +1272,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đạo đức 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Quang Dũng</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Bộ môn Dinh dưỡng - ĐH Y Hà Nội</t>
         </is>
       </c>
       <c r="F39">
-        <f>IF(ISBLANK(C39), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C39), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 3 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F40">
@@ -1316,12 +1319,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C08</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 4 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đạo đức 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F41">
@@ -1332,48 +1335,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C09</t>
+          <t>C08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đạo đức 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Hoàng Hà Linh</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
+          <t>Ủy viên HĐ Đạo đức 4 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F42">
-        <f>IF(ISBLANK(C42), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C42), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đạo đức 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Đạo đức 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Trương Phan Hồng Hà</t>
+          <t>Hoàng Hà Linh</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -1383,7 +1371,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
       <c r="F43">
@@ -1392,76 +1380,76 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Đạo đức 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Trương Phan Hồng Hà</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+      <c r="F44">
+        <f>IF(ISBLANK(C44), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>SEC_D</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>PHẦN D: HỘI ĐỒNG KHOA HỌC XÉT DUYỆT ĐỀ CƯƠNG (HĐ 02 - 7 THÀNH VIÊN BẮT BUỘC)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>D01</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Chủ tịch HĐ Đề cương (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Nguyễn Công Khẩn</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>GS.TS.</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
-        </is>
-      </c>
-      <c r="F45">
-        <f>IF(ISBLANK(C45), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Chủ tịch HĐ Đề cương (Bắt buộc)</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Xuân Ninh</t>
+          <t>Nguyễn Công Khẩn</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>GS.TS.</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
         </is>
       </c>
       <c r="F46">
@@ -1472,27 +1460,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Trần Quang Trung</t>
+          <t>Nguyễn Xuân Ninh</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Hiệp hội Sữa Việt Nam</t>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
         </is>
       </c>
       <c r="F47">
@@ -1503,27 +1491,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Lê Bạch Mai</t>
+          <t>Trần Quang Trung</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>PGS.TS.</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+          <t>Hiệp hội Sữa Việt Nam</t>
         </is>
       </c>
       <c r="F48">
@@ -1534,17 +1522,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Đề cương 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Lâm</t>
+          <t>Lê Bạch Mai</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -1565,28 +1553,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đề cương 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Lâm</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
         </is>
       </c>
       <c r="F50">
-        <f>IF(ISBLANK(C50), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C50), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>D07</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 3 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F51">
@@ -1597,12 +1600,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 4 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đề cương 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F52">
@@ -1613,48 +1616,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>D09</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đề cương 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Hoàng Hà Linh</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
+          <t>Ủy viên HĐ Đề cương 4 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F53">
-        <f>IF(ISBLANK(C53), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C53), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đề cương 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Đề cương 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Trương Phan Hồng Hà</t>
+          <t>Hoàng Hà Linh</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -1664,7 +1652,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
       <c r="F54">
@@ -1673,76 +1661,76 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Đề cương 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Trương Phan Hồng Hà</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+      <c r="F55">
+        <f>IF(ISBLANK(C55), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>SEC_E</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>PHẦN E: HỘI ĐỒNG ĐÁNH GIÁ NGHIỆM THU (HĐ 03 - 7 THÀNH VIÊN BẮT BUỘC)</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
-      <c r="F55" s="2" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Chủ tịch HĐ Nghiệm thu (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>Phạm Văn Hoàn</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>PGS.TS.</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
-        </is>
-      </c>
-      <c r="F56">
-        <f>IF(ISBLANK(C56), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Chủ tịch HĐ Nghiệm thu (Bắt buộc)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Công Khẩn</t>
+          <t>Phạm Văn Hoàn</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>GS.TS.</t>
+          <t>PGS.TS.</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
         </is>
       </c>
       <c r="F57">
@@ -1753,27 +1741,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Lâm</t>
+          <t>Nguyễn Công Khẩn</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>GS.TS.</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
         </is>
       </c>
       <c r="F58">
@@ -1784,27 +1772,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Ninh Thị Nhung</t>
+          <t>Nguyễn Thị Lâm</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Trường Đại học Y Dược Thái Bình</t>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
         </is>
       </c>
       <c r="F59">
@@ -1815,17 +1803,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Nghiệm thu 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Trần Văn Ơn</t>
+          <t>Ninh Thị Nhung</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -1835,7 +1823,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Trường Đại học Dược Hà Nội</t>
+          <t>Trường Đại học Y Dược Thái Bình</t>
         </is>
       </c>
       <c r="F60">
@@ -1846,28 +1834,43 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Nghiệm thu 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Trần Văn Ơn</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Trường Đại học Dược Hà Nội</t>
         </is>
       </c>
       <c r="F61">
-        <f>IF(ISBLANK(C61), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C61), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 3 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F62">
@@ -1878,12 +1881,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 4 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Nghiệm thu 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F63">
@@ -1894,53 +1897,38 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Nghiệm thu 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Hoàng Hà Linh</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>PGS.TS.BS.</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Ủy viên HĐ Nghiệm thu 4 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F64">
-        <f>IF(ISBLANK(C64), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C64), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Nghiệm thu 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Nghiệm thu 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Trương Phan Hồng Hà</t>
+          <t>Hoàng Hà Linh</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Thạc sĩ</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -1954,92 +1942,92 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Nghiệm thu 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Trương Phan Hồng Hà</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+      <c r="F66">
+        <f>IF(ISBLANK(C66), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>SEC_F</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>PHẦN F: LÝ LỊCH KHOA HỌC CHUYÊN GIA (CV CHỦ NHIỆM BẮT BUỘC &amp; CV THÀNH VIÊN TÙY CHỌN)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>F01</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Hồ sơ Chủ nhiệm đề tài (Bắt buộc - File mặc định cho HĐ Đạo đức)</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Trương Hồng Sơn</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Chủ nhiệm đề tài</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>Lý lịch khoa học - Trương Hồng Sơn.docx</t>
-        </is>
-      </c>
-      <c r="F67">
-        <f>IF(ISBLANK(C67), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", IF(OR(ISBLANK(D67), ISBLANK(E67)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV Mặc định Đạo đức"))</f>
-        <v/>
-      </c>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hồ sơ Đồng Chủ nhiệm (Tùy chọn)</t>
+          <t>Hồ sơ Chủ nhiệm đề tài (Bắt buộc - File mặc định cho HĐ Đạo đức)</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Trương Hồng Sơn</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Chủ nhiệm đề tài</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Lý lịch khoa học - Trương Hồng Sơn.docx</t>
         </is>
       </c>
       <c r="F68">
-        <f>IF(ISBLANK(C68), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D68), ISBLANK(E68)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C68), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", IF(OR(ISBLANK(D68), ISBLANK(E68)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV Mặc định Đạo đức"))</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hồ sơ Thư ký Đề tài (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Lưu Liên Hương</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Thư ký Đề tài</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Lý lịch khoa học_Liên Hương-2023.docx</t>
+          <t>Hồ sơ Đồng Chủ nhiệm (Tùy chọn)</t>
         </is>
       </c>
       <c r="F69">
@@ -2050,12 +2038,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 4 (Tùy chọn)</t>
+          <t>Hồ sơ Thư ký Đề tài (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Lưu Liên Hương</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Thư ký Đề tài</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Lý lịch khoa học_Liên Hương-2023.docx</t>
         </is>
       </c>
       <c r="F70">
@@ -2066,12 +2069,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 5 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 4 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F71">
@@ -2082,12 +2085,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 6 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 5 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F72">
@@ -2098,12 +2101,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F07</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 7 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 6 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F73">
@@ -2114,12 +2117,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F08</t>
+          <t>F07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 8 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 7 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F74">
@@ -2130,12 +2133,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F09</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 9 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 8 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F75">
@@ -2146,16 +2149,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F10</t>
+          <t>F09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 10 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 9 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F76">
         <f>IF(ISBLANK(C76), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D76), ISBLANK(E76)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Hồ sơ Chuyên gia / Thành viên 10 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F77">
+        <f>IF(ISBLANK(C77), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D77), ISBLANK(E77)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
         <v/>
       </c>
     </row>
@@ -2174,7 +2193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2361,65 +2380,68 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Địa điểm triển khai nghiên cứu (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12">
+        <f>IF(ISBLANK(C12), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>SEC_B</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>PHẦN B: BAN CHỦ NHIỆM &amp; NGHIÊN CỨU VIÊN ĐỀ TÀI (TỐI ĐA 20 NGƯỜI)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Chủ nhiệm đề tài (CNĐT - Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13">
-        <f>IF(ISBLANK(C13), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Đồng Chủ nhiệm đề tài (Tùy chọn)</t>
-        </is>
-      </c>
+          <t>Chủ nhiệm đề tài (CNĐT - Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
       <c r="F14">
-        <f>IF(ISBLANK(C14), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C14), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Thư ký Đề tài (Khác Thư ký HĐ - Tùy chọn)</t>
+          <t>Đồng Chủ nhiệm đề tài (Tùy chọn)</t>
         </is>
       </c>
       <c r="F15">
@@ -2430,12 +2452,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 1</t>
+          <t>Thư ký Đề tài (Khác Thư ký HĐ - Tùy chọn)</t>
         </is>
       </c>
       <c r="F16">
@@ -2446,12 +2468,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 2</t>
+          <t>Nghiên cứu viên 1</t>
         </is>
       </c>
       <c r="F17">
@@ -2462,12 +2484,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B06</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 3</t>
+          <t>Nghiên cứu viên 2</t>
         </is>
       </c>
       <c r="F18">
@@ -2478,12 +2500,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B07</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 4</t>
+          <t>Nghiên cứu viên 3</t>
         </is>
       </c>
       <c r="F19">
@@ -2494,12 +2516,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B08</t>
+          <t>B07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 5</t>
+          <t>Nghiên cứu viên 4</t>
         </is>
       </c>
       <c r="F20">
@@ -2510,12 +2532,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B09</t>
+          <t>B08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 6</t>
+          <t>Nghiên cứu viên 5</t>
         </is>
       </c>
       <c r="F21">
@@ -2526,12 +2548,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B10</t>
+          <t>B09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 7</t>
+          <t>Nghiên cứu viên 6</t>
         </is>
       </c>
       <c r="F22">
@@ -2542,12 +2564,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>B10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 8</t>
+          <t>Nghiên cứu viên 7</t>
         </is>
       </c>
       <c r="F23">
@@ -2558,12 +2580,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 9</t>
+          <t>Nghiên cứu viên 8</t>
         </is>
       </c>
       <c r="F24">
@@ -2574,12 +2596,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B13</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 10</t>
+          <t>Nghiên cứu viên 9</t>
         </is>
       </c>
       <c r="F25">
@@ -2590,12 +2612,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>B13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 11</t>
+          <t>Nghiên cứu viên 10</t>
         </is>
       </c>
       <c r="F26">
@@ -2606,12 +2628,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B15</t>
+          <t>B14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 12</t>
+          <t>Nghiên cứu viên 11</t>
         </is>
       </c>
       <c r="F27">
@@ -2622,12 +2644,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B16</t>
+          <t>B15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 13</t>
+          <t>Nghiên cứu viên 12</t>
         </is>
       </c>
       <c r="F28">
@@ -2638,12 +2660,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B17</t>
+          <t>B16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 14</t>
+          <t>Nghiên cứu viên 13</t>
         </is>
       </c>
       <c r="F29">
@@ -2654,12 +2676,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B18</t>
+          <t>B17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 15</t>
+          <t>Nghiên cứu viên 14</t>
         </is>
       </c>
       <c r="F30">
@@ -2670,17 +2692,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B19</t>
+          <t>B18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 16</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>(Để trống tên theo quy định)</t>
+          <t>Nghiên cứu viên 15</t>
         </is>
       </c>
       <c r="F31">
@@ -2691,12 +2708,12 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B20</t>
+          <t>B19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 17</t>
+          <t>Nghiên cứu viên 16</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2710,49 +2727,51 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nghiên cứu viên 17</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>(Để trống tên theo quy định)</t>
+        </is>
+      </c>
+      <c r="F33">
+        <f>IF(ISBLANK(C33), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>SEC_C</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>PHẦN C: HỘI ĐỒNG ĐẠO ĐỨC TRONG NGHIÊN CỨU (HĐ 01 - 7 THÀNH VIÊN BẮT BUỘC)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Chủ tịch HĐ Đạo đức (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34">
-        <f>IF(ISBLANK(C34), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Chủ tịch HĐ Đạo đức (Bắt buộc)</t>
         </is>
       </c>
       <c r="C35" s="3" t="n"/>
@@ -2766,12 +2785,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C36" s="3" t="n"/>
@@ -2785,12 +2804,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
@@ -2804,12 +2823,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Đạo đức 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
@@ -2823,28 +2842,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
-        </is>
-      </c>
+          <t>Ủy viên HĐ Đạo đức 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
       <c r="F39">
-        <f>IF(ISBLANK(C39), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C39), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 3 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F40">
@@ -2855,12 +2877,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C08</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 4 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đạo đức 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F41">
@@ -2871,31 +2893,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C09</t>
+          <t>C08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đạo đức 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
+          <t>Ủy viên HĐ Đạo đức 4 (Tùy chọn)</t>
+        </is>
+      </c>
       <c r="F42">
-        <f>IF(ISBLANK(C42), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C42), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đạo đức 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Đạo đức 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C43" s="3" t="n"/>
@@ -2907,49 +2926,49 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Đạo đức 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44">
+        <f>IF(ISBLANK(C44), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>SEC_D</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>PHẦN D: HỘI ĐỒNG KHOA HỌC XÉT DUYỆT ĐỀ CƯƠNG (HĐ 02 - 7 THÀNH VIÊN BẮT BUỘC)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>D01</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Chủ tịch HĐ Đề cương (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45">
-        <f>IF(ISBLANK(C45), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Chủ tịch HĐ Đề cương (Bắt buộc)</t>
         </is>
       </c>
       <c r="C46" s="3" t="n"/>
@@ -2963,12 +2982,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C47" s="3" t="n"/>
@@ -2982,12 +3001,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C48" s="3" t="n"/>
@@ -3001,12 +3020,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Đề cương 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C49" s="3" t="n"/>
@@ -3020,28 +3039,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
-        </is>
-      </c>
+          <t>Ủy viên HĐ Đề cương 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n"/>
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="n"/>
       <c r="F50">
-        <f>IF(ISBLANK(C50), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C50), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>D07</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 3 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F51">
@@ -3052,12 +3074,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 4 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đề cương 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F52">
@@ -3068,31 +3090,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>D09</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đề cương 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
+          <t>Ủy viên HĐ Đề cương 4 (Tùy chọn)</t>
+        </is>
+      </c>
       <c r="F53">
-        <f>IF(ISBLANK(C53), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C53), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đề cương 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Đề cương 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C54" s="3" t="n"/>
@@ -3104,49 +3123,49 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Đề cương 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55">
+        <f>IF(ISBLANK(C55), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>SEC_E</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>PHẦN E: HỘI ĐỒNG ĐÁNH GIÁ NGHIỆM THU (HĐ 03 - 7 THÀNH VIÊN BẮT BUỘC)</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="n"/>
-      <c r="F55" s="2" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Chủ tịch HĐ Nghiệm thu (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56">
-        <f>IF(ISBLANK(C56), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Chủ tịch HĐ Nghiệm thu (Bắt buộc)</t>
         </is>
       </c>
       <c r="C57" s="3" t="n"/>
@@ -3160,12 +3179,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C58" s="3" t="n"/>
@@ -3179,12 +3198,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C59" s="3" t="n"/>
@@ -3198,12 +3217,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Nghiệm thu 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C60" s="3" t="n"/>
@@ -3217,28 +3236,31 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
-        </is>
-      </c>
+          <t>Ủy viên HĐ Nghiệm thu 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n"/>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n"/>
       <c r="F61">
-        <f>IF(ISBLANK(C61), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C61), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 3 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F62">
@@ -3249,12 +3271,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 4 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Nghiệm thu 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F63">
@@ -3265,31 +3287,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Nghiệm thu 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="3" t="n"/>
+          <t>Ủy viên HĐ Nghiệm thu 4 (Tùy chọn)</t>
+        </is>
+      </c>
       <c r="F64">
-        <f>IF(ISBLANK(C64), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C64), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Nghiệm thu 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Nghiệm thu 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C65" s="3" t="n"/>
@@ -3301,65 +3320,68 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Nghiệm thu 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66">
+        <f>IF(ISBLANK(C66), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>SEC_F</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>PHẦN F: LÝ LỊCH KHOA HỌC CHUYÊN GIA (CV CHỦ NHIỆM BẮT BUỘC &amp; CV THÀNH VIÊN TÙY CHỌN)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>F01</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Hồ sơ Chủ nhiệm đề tài (Bắt buộc - File mặc định cho HĐ Đạo đức)</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
-      <c r="F67">
-        <f>IF(ISBLANK(C67), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", IF(OR(ISBLANK(D67), ISBLANK(E67)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV Mặc định Đạo đức"))</f>
-        <v/>
-      </c>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hồ sơ Đồng Chủ nhiệm (Tùy chọn)</t>
-        </is>
-      </c>
+          <t>Hồ sơ Chủ nhiệm đề tài (Bắt buộc - File mặc định cho HĐ Đạo đức)</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n"/>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
       <c r="F68">
-        <f>IF(ISBLANK(C68), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D68), ISBLANK(E68)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C68), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", IF(OR(ISBLANK(D68), ISBLANK(E68)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV Mặc định Đạo đức"))</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hồ sơ Thư ký Đề tài (Tùy chọn)</t>
+          <t>Hồ sơ Đồng Chủ nhiệm (Tùy chọn)</t>
         </is>
       </c>
       <c r="F69">
@@ -3370,12 +3392,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 4 (Tùy chọn)</t>
+          <t>Hồ sơ Thư ký Đề tài (Tùy chọn)</t>
         </is>
       </c>
       <c r="F70">
@@ -3386,12 +3408,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 5 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 4 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F71">
@@ -3402,12 +3424,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 6 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 5 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F72">
@@ -3418,12 +3440,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F07</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 7 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 6 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F73">
@@ -3434,12 +3456,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F08</t>
+          <t>F07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 8 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 7 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F74">
@@ -3450,12 +3472,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F09</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 9 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 8 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F75">
@@ -3466,16 +3488,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F10</t>
+          <t>F09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 10 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 9 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F76">
         <f>IF(ISBLANK(C76), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D76), ISBLANK(E76)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Hồ sơ Chuyên gia / Thành viên 10 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F77">
+        <f>IF(ISBLANK(C77), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D77), ISBLANK(E77)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
         <v/>
       </c>
     </row>

--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -2077,6 +2077,21 @@
           <t>Hồ sơ Chuyên gia / Thành viên 4 (Tùy chọn)</t>
         </is>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Nguyễn Công Khẩn</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Chuyên gia hội đồng</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>TM-Gs. Nguyen Cong Khan.pdf</t>
+        </is>
+      </c>
       <c r="F71">
         <f>IF(ISBLANK(C71), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D71), ISBLANK(E71)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
         <v/>
@@ -2093,6 +2108,21 @@
           <t>Hồ sơ Chuyên gia / Thành viên 5 (Tùy chọn)</t>
         </is>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Hoàng Thị Thanh</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Chuyên gia hội đồng</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>TM-PGs. Hoang Thi Thanh.pdf</t>
+        </is>
+      </c>
       <c r="F72">
         <f>IF(ISBLANK(C72), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D72), ISBLANK(E72)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
         <v/>
@@ -2109,6 +2139,21 @@
           <t>Hồ sơ Chuyên gia / Thành viên 6 (Tùy chọn)</t>
         </is>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Nguyễn Quang Dũng</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Chuyên gia hội đồng</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>TM-PGs. Nguyen Quang Dung.pdf</t>
+        </is>
+      </c>
       <c r="F73">
         <f>IF(ISBLANK(C73), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D73), ISBLANK(E73)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
         <v/>
@@ -2125,6 +2170,21 @@
           <t>Hồ sơ Chuyên gia / Thành viên 7 (Tùy chọn)</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Trần Quang Trung</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Chuyên gia hội đồng</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>TM-PGs. Tran Quang Trung.pdf</t>
+        </is>
+      </c>
       <c r="F74">
         <f>IF(ISBLANK(C74), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D74), ISBLANK(E74)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
         <v/>
@@ -2139,6 +2199,21 @@
       <c r="B75" t="inlineStr">
         <is>
           <t>Hồ sơ Chuyên gia / Thành viên 8 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Nguyễn Hùng Long</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Chuyên gia hội đồng</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>TM-Ts. Nguyen Hung Long.pdf</t>
         </is>
       </c>
       <c r="F75">

--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -2056,11 +2056,6 @@
           <t>Thư ký Đề tài</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Lý lịch khoa học_Liên Hương-2023.docx</t>
-        </is>
-      </c>
       <c r="F70">
         <f>IF(ISBLANK(C70), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D70), ISBLANK(E70)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
         <v/>

--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Bánh ăn dặm VIAM 2027" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Mẫu trắng dự án mới" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -3592,6 +3593,70 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="E68 E69 E70 E71 E72 E73 E74 E75 E76 E77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='_Lists'!$A$1:$A$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TVCT_ĐGHQ,TNLS"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Lý lịch khoa học - Trương Hồng Sơn.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TM-Gs. Nguyen Cong Khan.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TM-PGs. Hoang Thi Thanh.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TM-PGs. Nguyen Quang Dung.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TM-PGs. Tran Quang Trung.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TM-Ts. Nguyen Hung Long.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Bánh ăn dặm VIAM 2027" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Mẫu trắng dự án mới" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Lists" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tokens" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -3659,4 +3660,325 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>token_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TEN_DE_TAI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Tên đề tài</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NAM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Năm thực hiện hồ sơ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DON_VI_CHU_TRI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cơ quan chủ trì</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DON_VI_DOI_TAC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cơ quan phối hợp</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CHU_NHIEM_HO_TEN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>person_ho_ten</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Chủ nhiệm đề tài - có học hàm/học vị</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CHU_NHIEM_TEN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>person_ten</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Chủ nhiệm đề tài - chỉ tên</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DONG_CHU_NHIEM_TEN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B02</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>person_ten</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Đồng chủ nhiệm đề tài - chỉ tên</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DONG_CHU_NHIEM_HO_TEN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B02</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>person_ho_ten</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Đồng chủ nhiệm đề tài - có học hàm/học vị</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>THU_KY_DE_TAI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>person_ho_ten</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Thư ký đề tài</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>THOI_GIAN_BAT_DAU</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>timeline_start</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mốc bắt đầu (MM/YYYY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>THOI_GIAN_KET_THUC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>timeline_end</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Mốc kết thúc (MM/YYYY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DIA_DIEM_TRIEN_KHAI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>raw_or_placeholder</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>……………………………</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Địa điểm triển khai nghiên cứu</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Mẫu trắng dự án mới" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Lists" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tokens" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_NhanSu" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -3714,7 +3715,6 @@
           <t>raw</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Tên đề tài</t>
@@ -3737,7 +3737,6 @@
           <t>raw</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Năm thực hiện hồ sơ</t>
@@ -3760,7 +3759,6 @@
           <t>raw</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Cơ quan chủ trì</t>
@@ -3783,7 +3781,6 @@
           <t>raw</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Cơ quan phối hợp</t>
@@ -3806,7 +3803,6 @@
           <t>person_ho_ten</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Chủ nhiệm đề tài - có học hàm/học vị</t>
@@ -3829,7 +3825,6 @@
           <t>person_ten</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Chủ nhiệm đề tài - chỉ tên</t>
@@ -3852,7 +3847,6 @@
           <t>person_ten</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Đồng chủ nhiệm đề tài - chỉ tên</t>
@@ -3875,7 +3869,6 @@
           <t>person_ho_ten</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Đồng chủ nhiệm đề tài - có học hàm/học vị</t>
@@ -3898,7 +3891,6 @@
           <t>person_ho_ten</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Thư ký đề tài</t>
@@ -3921,7 +3913,6 @@
           <t>timeline_start</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Mốc bắt đầu (MM/YYYY)</t>
@@ -3944,7 +3935,6 @@
           <t>timeline_end</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Mốc kết thúc (MM/YYYY)</t>
@@ -3975,6 +3965,327 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>Địa điểm triển khai nghiên cứu</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ten</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>hoc_ham_hoc_vi</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>dia_chi</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sdt</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>cccd</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>mst</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>so_tk</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ngan_hang</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Trương Hồng Sơn</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TS.BS.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Viện trưởng - Viện Y học Ứng dụng VN</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lưu Liên Hương</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Trung tâm NCKH - Viện VIAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lê Việt Anh</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Trung tâm NCKH - Viện VIAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lê Minh Khánh</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bác sĩ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Phòng khám VIAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nguyễn Công Khẩn</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GS.TS.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nguyễn Xuân Ninh</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lê Bạch Mai</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Lâm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Nguyễn Quang Dũng</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bộ môn Dinh dưỡng - ĐH Y Hà Nội</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hoàng Hà Linh</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Trung tâm NCKH - Viện VIAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Trương Phan Hồng Hà</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Trần Quang Trung</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hiệp hội Sữa Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Phạm Văn Hoàn</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ninh Thị Nhung</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trường Đại học Y Dược Thái Bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Trần Văn Ơn</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trường Đại học Dược Hà Nội</t>
         </is>
       </c>
     </row>

--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -2049,16 +2049,6 @@
           <t>Hồ sơ Thư ký Đề tài (Tùy chọn)</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Lưu Liên Hương</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Thư ký Đề tài</t>
-        </is>
-      </c>
       <c r="F70">
         <f>IF(ISBLANK(C70), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D70), ISBLANK(E70)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
         <v/>

--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -9,8 +9,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Bánh ăn dặm VIAM 2027" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Mẫu trắng dự án mới" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Lists" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tokens" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_NhanSu" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_NhanSu" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tokens" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -737,92 +737,80 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Đầu mối liên hệ (họ tên, đơn vị, email, điện thoại - Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13">
+        <f>IF(ISBLANK(C13), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>SEC_B</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>PHẦN B: BAN CHỦ NHIỆM &amp; NGHIÊN CỨU VIÊN ĐỀ TÀI (TỐI ĐA 20 NGƯỜI)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Chủ nhiệm đề tài (CNĐT - Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Trương Hồng Sơn</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>TS.BS.</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Viện trưởng - Viện Y học Ứng dụng VN</t>
-        </is>
-      </c>
-      <c r="F14">
-        <f>IF(ISBLANK(C14), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Đồng Chủ nhiệm đề tài (Tùy chọn)</t>
+          <t>Chủ nhiệm đề tài (CNĐT - Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Trương Hồng Sơn</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>TS.BS.</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Viện trưởng - Viện Y học Ứng dụng VN</t>
         </is>
       </c>
       <c r="F15">
-        <f>IF(ISBLANK(C15), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C15), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thư ký Đề tài (Khác Thư ký HĐ - Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Lưu Liên Hương</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
+          <t>Đồng Chủ nhiệm đề tài (Tùy chọn)</t>
         </is>
       </c>
       <c r="F16">
@@ -833,17 +821,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 1</t>
+          <t>Thư ký Đề tài (Khác Thư ký HĐ - Tùy chọn)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lê Việt Anh</t>
+          <t>Lưu Liên Hương</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -864,27 +852,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 2</t>
+          <t>Nghiên cứu viên 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lê Minh Khánh</t>
+          <t>Lê Việt Anh</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bác sĩ</t>
+          <t>Thạc sĩ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Phòng khám VIAM</t>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
       <c r="F18">
@@ -895,12 +883,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B06</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 3</t>
+          <t>Nghiên cứu viên 2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Lê Minh Khánh</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bác sĩ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Phòng khám VIAM</t>
         </is>
       </c>
       <c r="F19">
@@ -911,12 +914,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B07</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 4</t>
+          <t>Nghiên cứu viên 3</t>
         </is>
       </c>
       <c r="F20">
@@ -927,12 +930,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B08</t>
+          <t>B07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 5</t>
+          <t>Nghiên cứu viên 4</t>
         </is>
       </c>
       <c r="F21">
@@ -943,12 +946,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B09</t>
+          <t>B08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 6</t>
+          <t>Nghiên cứu viên 5</t>
         </is>
       </c>
       <c r="F22">
@@ -959,12 +962,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B10</t>
+          <t>B09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 7</t>
+          <t>Nghiên cứu viên 6</t>
         </is>
       </c>
       <c r="F23">
@@ -975,12 +978,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>B10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 8</t>
+          <t>Nghiên cứu viên 7</t>
         </is>
       </c>
       <c r="F24">
@@ -991,12 +994,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 9</t>
+          <t>Nghiên cứu viên 8</t>
         </is>
       </c>
       <c r="F25">
@@ -1007,12 +1010,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B13</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 10</t>
+          <t>Nghiên cứu viên 9</t>
         </is>
       </c>
       <c r="F26">
@@ -1023,12 +1026,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>B13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 11</t>
+          <t>Nghiên cứu viên 10</t>
         </is>
       </c>
       <c r="F27">
@@ -1039,12 +1042,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B15</t>
+          <t>B14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 12</t>
+          <t>Nghiên cứu viên 11</t>
         </is>
       </c>
       <c r="F28">
@@ -1055,12 +1058,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B16</t>
+          <t>B15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 13</t>
+          <t>Nghiên cứu viên 12</t>
         </is>
       </c>
       <c r="F29">
@@ -1071,12 +1074,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B17</t>
+          <t>B16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 14</t>
+          <t>Nghiên cứu viên 13</t>
         </is>
       </c>
       <c r="F30">
@@ -1087,12 +1090,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B18</t>
+          <t>B17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 15</t>
+          <t>Nghiên cứu viên 14</t>
         </is>
       </c>
       <c r="F31">
@@ -1103,12 +1106,12 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B19</t>
+          <t>B18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 16</t>
+          <t>Nghiên cứu viên 15</t>
         </is>
       </c>
       <c r="F32">
@@ -1119,12 +1122,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B20</t>
+          <t>B19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 17</t>
+          <t>Nghiên cứu viên 16</t>
         </is>
       </c>
       <c r="F33">
@@ -1133,76 +1136,61 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nghiên cứu viên 17</t>
+        </is>
+      </c>
+      <c r="F34">
+        <f>IF(ISBLANK(C34), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>SEC_C</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>PHẦN C: HỘI ĐỒNG ĐẠO ĐỨC TRONG NGHIÊN CỨU (HĐ 01 - 7 THÀNH VIÊN BẮT BUỘC)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Chủ tịch HĐ Đạo đức (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Nguyễn Công Khẩn</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>GS.TS.</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
-        </is>
-      </c>
-      <c r="F35">
-        <f>IF(ISBLANK(C35), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Chủ tịch HĐ Đạo đức (Bắt buộc)</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Xuân Ninh</t>
+          <t>Nguyễn Công Khẩn</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>GS.TS.</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
         </is>
       </c>
       <c r="F36">
@@ -1213,17 +1201,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Lê Bạch Mai</t>
+          <t>Nguyễn Xuân Ninh</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1233,7 +1221,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
         </is>
       </c>
       <c r="F37">
@@ -1244,17 +1232,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Lâm</t>
+          <t>Lê Bạch Mai</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -1275,17 +1263,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Đạo đức 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Quang Dũng</t>
+          <t>Nguyễn Thị Lâm</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -1295,7 +1283,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Bộ môn Dinh dưỡng - ĐH Y Hà Nội</t>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
         </is>
       </c>
       <c r="F39">
@@ -1306,28 +1294,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đạo đức 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Quang Dũng</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Bộ môn Dinh dưỡng - ĐH Y Hà Nội</t>
         </is>
       </c>
       <c r="F40">
-        <f>IF(ISBLANK(C40), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C40), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 3 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F41">
@@ -1338,12 +1341,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C08</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 4 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đạo đức 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F42">
@@ -1354,48 +1357,33 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C09</t>
+          <t>C08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đạo đức 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Hoàng Hà Linh</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
+          <t>Ủy viên HĐ Đạo đức 4 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F43">
-        <f>IF(ISBLANK(C43), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C43), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đạo đức 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Đạo đức 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Trương Phan Hồng Hà</t>
+          <t>Hoàng Hà Linh</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -1405,7 +1393,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
       <c r="F44">
@@ -1414,76 +1402,76 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Đạo đức 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Trương Phan Hồng Hà</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+      <c r="F45">
+        <f>IF(ISBLANK(C45), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>SEC_D</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>PHẦN D: HỘI ĐỒNG KHOA HỌC XÉT DUYỆT ĐỀ CƯƠNG (HĐ 02 - 7 THÀNH VIÊN BẮT BUỘC)</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>D01</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Chủ tịch HĐ Đề cương (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Nguyễn Công Khẩn</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>GS.TS.</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
-        </is>
-      </c>
-      <c r="F46">
-        <f>IF(ISBLANK(C46), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Chủ tịch HĐ Đề cương (Bắt buộc)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Xuân Ninh</t>
+          <t>Nguyễn Công Khẩn</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>GS.TS.</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
         </is>
       </c>
       <c r="F47">
@@ -1494,27 +1482,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Trần Quang Trung</t>
+          <t>Nguyễn Xuân Ninh</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Hiệp hội Sữa Việt Nam</t>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
         </is>
       </c>
       <c r="F48">
@@ -1525,27 +1513,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Lê Bạch Mai</t>
+          <t>Trần Quang Trung</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>PGS.TS.</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+          <t>Hiệp hội Sữa Việt Nam</t>
         </is>
       </c>
       <c r="F49">
@@ -1556,17 +1544,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Đề cương 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Lâm</t>
+          <t>Lê Bạch Mai</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -1587,28 +1575,43 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đề cương 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Lâm</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
         </is>
       </c>
       <c r="F51">
-        <f>IF(ISBLANK(C51), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C51), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>D07</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 3 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F52">
@@ -1619,12 +1622,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 4 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đề cương 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F53">
@@ -1635,48 +1638,33 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>D09</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đề cương 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Hoàng Hà Linh</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
+          <t>Ủy viên HĐ Đề cương 4 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F54">
-        <f>IF(ISBLANK(C54), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C54), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đề cương 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Đề cương 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Trương Phan Hồng Hà</t>
+          <t>Hoàng Hà Linh</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -1686,7 +1674,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
       <c r="F55">
@@ -1695,76 +1683,76 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Đề cương 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Trương Phan Hồng Hà</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+      <c r="F56">
+        <f>IF(ISBLANK(C56), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>SEC_E</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>PHẦN E: HỘI ĐỒNG ĐÁNH GIÁ NGHIỆM THU (HĐ 03 - 7 THÀNH VIÊN BẮT BUỘC)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Chủ tịch HĐ Nghiệm thu (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>Phạm Văn Hoàn</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>PGS.TS.</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
-        </is>
-      </c>
-      <c r="F57">
-        <f>IF(ISBLANK(C57), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Chủ tịch HĐ Nghiệm thu (Bắt buộc)</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Công Khẩn</t>
+          <t>Phạm Văn Hoàn</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>GS.TS.</t>
+          <t>PGS.TS.</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
         </is>
       </c>
       <c r="F58">
@@ -1775,27 +1763,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Lâm</t>
+          <t>Nguyễn Công Khẩn</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>GS.TS.</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
         </is>
       </c>
       <c r="F59">
@@ -1806,27 +1794,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Ninh Thị Nhung</t>
+          <t>Nguyễn Thị Lâm</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Trường Đại học Y Dược Thái Bình</t>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
         </is>
       </c>
       <c r="F60">
@@ -1837,17 +1825,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Nghiệm thu 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Trần Văn Ơn</t>
+          <t>Ninh Thị Nhung</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -1857,7 +1845,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Trường Đại học Dược Hà Nội</t>
+          <t>Trường Đại học Y Dược Thái Bình</t>
         </is>
       </c>
       <c r="F61">
@@ -1868,28 +1856,43 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Nghiệm thu 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Trần Văn Ơn</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Trường Đại học Dược Hà Nội</t>
         </is>
       </c>
       <c r="F62">
-        <f>IF(ISBLANK(C62), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C62), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 3 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F63">
@@ -1900,12 +1903,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 4 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Nghiệm thu 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F64">
@@ -1916,53 +1919,38 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Nghiệm thu 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>Hoàng Hà Linh</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>PGS.TS.BS.</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Ủy viên HĐ Nghiệm thu 4 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F65">
-        <f>IF(ISBLANK(C65), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C65), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Nghiệm thu 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Nghiệm thu 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Trương Phan Hồng Hà</t>
+          <t>Hoàng Hà Linh</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Thạc sĩ</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -1976,77 +1964,92 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Nghiệm thu 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Trương Phan Hồng Hà</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+      <c r="F67">
+        <f>IF(ISBLANK(C67), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>SEC_F</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>PHẦN F: LÝ LỊCH KHOA HỌC CHUYÊN GIA (CV CHỦ NHIỆM BẮT BUỘC &amp; CV THÀNH VIÊN TÙY CHỌN)</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>F01</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Hồ sơ Chủ nhiệm đề tài (Bắt buộc - File mặc định cho HĐ Đạo đức)</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Trương Hồng Sơn</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Chủ nhiệm đề tài</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>Lý lịch khoa học - Trương Hồng Sơn.docx</t>
-        </is>
-      </c>
-      <c r="F68">
-        <f>IF(ISBLANK(C68), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", IF(OR(ISBLANK(D68), ISBLANK(E68)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV Mặc định Đạo đức"))</f>
-        <v/>
-      </c>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hồ sơ Đồng Chủ nhiệm (Tùy chọn)</t>
+          <t>Hồ sơ Chủ nhiệm đề tài (Bắt buộc - File mặc định cho HĐ Đạo đức)</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Trương Hồng Sơn</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Chủ nhiệm đề tài</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Lý lịch khoa học - Trương Hồng Sơn.docx</t>
         </is>
       </c>
       <c r="F69">
-        <f>IF(ISBLANK(C69), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D69), ISBLANK(E69)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C69), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", IF(OR(ISBLANK(D69), ISBLANK(E69)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV Mặc định Đạo đức"))</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hồ sơ Thư ký Đề tài (Tùy chọn)</t>
+          <t>Hồ sơ Đồng Chủ nhiệm (Tùy chọn)</t>
         </is>
       </c>
       <c r="F70">
@@ -2057,27 +2060,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 4 (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Nguyễn Công Khẩn</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Chuyên gia hội đồng</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>TM-Gs. Nguyen Cong Khan.pdf</t>
+          <t>Hồ sơ Thư ký Đề tài (Tùy chọn)</t>
         </is>
       </c>
       <c r="F71">
@@ -2088,17 +2076,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 5 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 4 (Tùy chọn)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hoàng Thị Thanh</t>
+          <t>Nguyễn Công Khẩn</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2108,7 +2096,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TM-PGs. Hoang Thi Thanh.pdf</t>
+          <t>TM-Gs. Nguyen Cong Khan.pdf</t>
         </is>
       </c>
       <c r="F72">
@@ -2119,17 +2107,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 6 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 5 (Tùy chọn)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nguyễn Quang Dũng</t>
+          <t>Hoàng Thị Thanh</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2139,7 +2127,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>TM-PGs. Nguyen Quang Dung.pdf</t>
+          <t>TM-PGs. Hoang Thi Thanh.pdf</t>
         </is>
       </c>
       <c r="F73">
@@ -2150,17 +2138,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F07</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 7 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 6 (Tùy chọn)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Trần Quang Trung</t>
+          <t>Nguyễn Quang Dũng</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2170,7 +2158,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TM-PGs. Tran Quang Trung.pdf</t>
+          <t>TM-PGs. Nguyen Quang Dung.pdf</t>
         </is>
       </c>
       <c r="F74">
@@ -2181,17 +2169,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F08</t>
+          <t>F07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 8 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 7 (Tùy chọn)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nguyễn Hùng Long</t>
+          <t>Trần Quang Trung</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2201,7 +2189,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>TM-Ts. Nguyen Hung Long.pdf</t>
+          <t>TM-PGs. Tran Quang Trung.pdf</t>
         </is>
       </c>
       <c r="F75">
@@ -2212,12 +2200,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F09</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 9 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 8 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Nguyễn Hùng Long</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Chuyên gia hội đồng</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>TM-Ts. Nguyen Hung Long.pdf</t>
         </is>
       </c>
       <c r="F76">
@@ -2228,16 +2231,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>F10</t>
+          <t>F09</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 10 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 9 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F77">
         <f>IF(ISBLANK(C77), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D77), ISBLANK(E77)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Hồ sơ Chuyên gia / Thành viên 10 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F78">
+        <f>IF(ISBLANK(C78), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D78), ISBLANK(E78)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
         <v/>
       </c>
     </row>
@@ -2256,7 +2275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2462,65 +2481,68 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Đầu mối liên hệ (họ tên, đơn vị, email, điện thoại - Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13">
+        <f>IF(ISBLANK(C13), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>SEC_B</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>PHẦN B: BAN CHỦ NHIỆM &amp; NGHIÊN CỨU VIÊN ĐỀ TÀI (TỐI ĐA 20 NGƯỜI)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Chủ nhiệm đề tài (CNĐT - Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14">
-        <f>IF(ISBLANK(C14), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Đồng Chủ nhiệm đề tài (Tùy chọn)</t>
-        </is>
-      </c>
+          <t>Chủ nhiệm đề tài (CNĐT - Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
       <c r="F15">
-        <f>IF(ISBLANK(C15), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C15), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thư ký Đề tài (Khác Thư ký HĐ - Tùy chọn)</t>
+          <t>Đồng Chủ nhiệm đề tài (Tùy chọn)</t>
         </is>
       </c>
       <c r="F16">
@@ -2531,12 +2553,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 1</t>
+          <t>Thư ký Đề tài (Khác Thư ký HĐ - Tùy chọn)</t>
         </is>
       </c>
       <c r="F17">
@@ -2547,12 +2569,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B05</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 2</t>
+          <t>Nghiên cứu viên 1</t>
         </is>
       </c>
       <c r="F18">
@@ -2563,12 +2585,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B06</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 3</t>
+          <t>Nghiên cứu viên 2</t>
         </is>
       </c>
       <c r="F19">
@@ -2579,12 +2601,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B07</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 4</t>
+          <t>Nghiên cứu viên 3</t>
         </is>
       </c>
       <c r="F20">
@@ -2595,12 +2617,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B08</t>
+          <t>B07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 5</t>
+          <t>Nghiên cứu viên 4</t>
         </is>
       </c>
       <c r="F21">
@@ -2611,12 +2633,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B09</t>
+          <t>B08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 6</t>
+          <t>Nghiên cứu viên 5</t>
         </is>
       </c>
       <c r="F22">
@@ -2627,12 +2649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B10</t>
+          <t>B09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 7</t>
+          <t>Nghiên cứu viên 6</t>
         </is>
       </c>
       <c r="F23">
@@ -2643,12 +2665,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>B10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 8</t>
+          <t>Nghiên cứu viên 7</t>
         </is>
       </c>
       <c r="F24">
@@ -2659,12 +2681,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 9</t>
+          <t>Nghiên cứu viên 8</t>
         </is>
       </c>
       <c r="F25">
@@ -2675,12 +2697,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B13</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 10</t>
+          <t>Nghiên cứu viên 9</t>
         </is>
       </c>
       <c r="F26">
@@ -2691,12 +2713,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>B13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 11</t>
+          <t>Nghiên cứu viên 10</t>
         </is>
       </c>
       <c r="F27">
@@ -2707,12 +2729,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B15</t>
+          <t>B14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 12</t>
+          <t>Nghiên cứu viên 11</t>
         </is>
       </c>
       <c r="F28">
@@ -2723,12 +2745,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B16</t>
+          <t>B15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 13</t>
+          <t>Nghiên cứu viên 12</t>
         </is>
       </c>
       <c r="F29">
@@ -2739,12 +2761,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B17</t>
+          <t>B16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 14</t>
+          <t>Nghiên cứu viên 13</t>
         </is>
       </c>
       <c r="F30">
@@ -2755,12 +2777,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B18</t>
+          <t>B17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 15</t>
+          <t>Nghiên cứu viên 14</t>
         </is>
       </c>
       <c r="F31">
@@ -2771,17 +2793,12 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B19</t>
+          <t>B18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 16</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>(Để trống tên theo quy định)</t>
+          <t>Nghiên cứu viên 15</t>
         </is>
       </c>
       <c r="F32">
@@ -2792,12 +2809,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B20</t>
+          <t>B19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 17</t>
+          <t>Nghiên cứu viên 16</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2811,49 +2828,51 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nghiên cứu viên 17</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>(Để trống tên theo quy định)</t>
+        </is>
+      </c>
+      <c r="F34">
+        <f>IF(ISBLANK(C34), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>SEC_C</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>PHẦN C: HỘI ĐỒNG ĐẠO ĐỨC TRONG NGHIÊN CỨU (HĐ 01 - 7 THÀNH VIÊN BẮT BUỘC)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Chủ tịch HĐ Đạo đức (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35">
-        <f>IF(ISBLANK(C35), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Chủ tịch HĐ Đạo đức (Bắt buộc)</t>
         </is>
       </c>
       <c r="C36" s="3" t="n"/>
@@ -2867,12 +2886,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
@@ -2886,12 +2905,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
@@ -2905,12 +2924,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>C04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Đạo đức 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C39" s="3" t="n"/>
@@ -2924,28 +2943,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
-        </is>
-      </c>
+          <t>Ủy viên HĐ Đạo đức 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
       <c r="F40">
-        <f>IF(ISBLANK(C40), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C40), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 3 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F41">
@@ -2956,12 +2978,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C08</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 4 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đạo đức 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F42">
@@ -2972,31 +2994,28 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C09</t>
+          <t>C08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đạo đức 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n"/>
+          <t>Ủy viên HĐ Đạo đức 4 (Tùy chọn)</t>
+        </is>
+      </c>
       <c r="F43">
-        <f>IF(ISBLANK(C43), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C43), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đạo đức 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Đạo đức 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
@@ -3008,49 +3027,49 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Đạo đức 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45">
+        <f>IF(ISBLANK(C45), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>SEC_D</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>PHẦN D: HỘI ĐỒNG KHOA HỌC XÉT DUYỆT ĐỀ CƯƠNG (HĐ 02 - 7 THÀNH VIÊN BẮT BUỘC)</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>D01</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Chủ tịch HĐ Đề cương (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46">
-        <f>IF(ISBLANK(C46), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Chủ tịch HĐ Đề cương (Bắt buộc)</t>
         </is>
       </c>
       <c r="C47" s="3" t="n"/>
@@ -3064,12 +3083,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C48" s="3" t="n"/>
@@ -3083,12 +3102,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C49" s="3" t="n"/>
@@ -3102,12 +3121,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Đề cương 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C50" s="3" t="n"/>
@@ -3121,28 +3140,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
-        </is>
-      </c>
+          <t>Ủy viên HĐ Đề cương 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n"/>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
       <c r="F51">
-        <f>IF(ISBLANK(C51), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C51), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>D07</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 3 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F52">
@@ -3153,12 +3175,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 4 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đề cương 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F53">
@@ -3169,31 +3191,28 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>D09</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đề cương 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="3" t="n"/>
+          <t>Ủy viên HĐ Đề cương 4 (Tùy chọn)</t>
+        </is>
+      </c>
       <c r="F54">
-        <f>IF(ISBLANK(C54), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C54), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đề cương 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Đề cương 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C55" s="3" t="n"/>
@@ -3205,49 +3224,49 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Đề cương 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56">
+        <f>IF(ISBLANK(C56), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>SEC_E</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>PHẦN E: HỘI ĐỒNG ĐÁNH GIÁ NGHIỆM THU (HĐ 03 - 7 THÀNH VIÊN BẮT BUỘC)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Chủ tịch HĐ Nghiệm thu (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="3" t="n"/>
-      <c r="F57">
-        <f>IF(ISBLANK(C57), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Chủ tịch HĐ Nghiệm thu (Bắt buộc)</t>
         </is>
       </c>
       <c r="C58" s="3" t="n"/>
@@ -3261,12 +3280,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C59" s="3" t="n"/>
@@ -3280,12 +3299,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C60" s="3" t="n"/>
@@ -3299,12 +3318,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Nghiệm thu 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C61" s="3" t="n"/>
@@ -3318,28 +3337,31 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
-        </is>
-      </c>
+          <t>Ủy viên HĐ Nghiệm thu 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n"/>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
       <c r="F62">
-        <f>IF(ISBLANK(C62), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C62), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 3 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F63">
@@ -3350,12 +3372,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 4 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Nghiệm thu 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F64">
@@ -3366,31 +3388,28 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Nghiệm thu 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="3" t="n"/>
+          <t>Ủy viên HĐ Nghiệm thu 4 (Tùy chọn)</t>
+        </is>
+      </c>
       <c r="F65">
-        <f>IF(ISBLANK(C65), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C65), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Nghiệm thu 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Nghiệm thu 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C66" s="3" t="n"/>
@@ -3402,65 +3421,68 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Nghiệm thu 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n"/>
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67">
+        <f>IF(ISBLANK(C67), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>SEC_F</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>PHẦN F: LÝ LỊCH KHOA HỌC CHUYÊN GIA (CV CHỦ NHIỆM BẮT BUỘC &amp; CV THÀNH VIÊN TÙY CHỌN)</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>F01</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Hồ sơ Chủ nhiệm đề tài (Bắt buộc - File mặc định cho HĐ Đạo đức)</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68">
-        <f>IF(ISBLANK(C68), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", IF(OR(ISBLANK(D68), ISBLANK(E68)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV Mặc định Đạo đức"))</f>
-        <v/>
-      </c>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>F02</t>
+          <t>F01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hồ sơ Đồng Chủ nhiệm (Tùy chọn)</t>
-        </is>
-      </c>
+          <t>Hồ sơ Chủ nhiệm đề tài (Bắt buộc - File mặc định cho HĐ Đạo đức)</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
       <c r="F69">
-        <f>IF(ISBLANK(C69), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D69), ISBLANK(E69)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C69), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", IF(OR(ISBLANK(D69), ISBLANK(E69)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV Mặc định Đạo đức"))</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>F03</t>
+          <t>F02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hồ sơ Thư ký Đề tài (Tùy chọn)</t>
+          <t>Hồ sơ Đồng Chủ nhiệm (Tùy chọn)</t>
         </is>
       </c>
       <c r="F70">
@@ -3471,12 +3493,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>F04</t>
+          <t>F03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 4 (Tùy chọn)</t>
+          <t>Hồ sơ Thư ký Đề tài (Tùy chọn)</t>
         </is>
       </c>
       <c r="F71">
@@ -3487,12 +3509,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>F04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 5 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 4 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F72">
@@ -3503,12 +3525,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 6 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 5 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F73">
@@ -3519,12 +3541,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F07</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 7 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 6 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F74">
@@ -3535,12 +3557,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F08</t>
+          <t>F07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 8 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 7 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F75">
@@ -3551,12 +3573,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F09</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 9 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 8 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F76">
@@ -3567,16 +3589,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>F10</t>
+          <t>F09</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 10 (Tùy chọn)</t>
+          <t>Hồ sơ Chuyên gia / Thành viên 9 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F77">
         <f>IF(ISBLANK(C77), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D77), ISBLANK(E77)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Hồ sơ Chuyên gia / Thành viên 10 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F78">
+        <f>IF(ISBLANK(C78), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D78), ISBLANK(E78)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
         <v/>
       </c>
     </row>
@@ -3659,302 +3697,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>token_name</t>
+          <t>ten</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>hoc_ham_hoc_vi</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>don_vi</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>param</t>
+          <t>dia_chi</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>sdt</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>cccd</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>mst</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>so_tk</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ngan_hang</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEN_DE_TAI</t>
+          <t>Trương Hồng Sơn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>TS.BS.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Tên đề tài</t>
+          <t>Viện trưởng - Viện Y học Ứng dụng VN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>Lưu Liên Hương</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>Thạc sĩ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Năm thực hiện hồ sơ</t>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DON_VI_CHU_TRI</t>
+          <t>Lê Việt Anh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>Thạc sĩ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Cơ quan chủ trì</t>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DON_VI_DOI_TAC</t>
+          <t>Lê Minh Khánh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>Bác sĩ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Cơ quan phối hợp</t>
+          <t>Phòng khám VIAM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHU_NHIEM_HO_TEN</t>
+          <t>Nguyễn Công Khẩn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>GS.TS.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>person_ho_ten</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Chủ nhiệm đề tài - có học hàm/học vị</t>
+          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHU_NHIEM_TEN</t>
+          <t>Nguyễn Xuân Ninh</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>person_ten</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Chủ nhiệm đề tài - chỉ tên</t>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DONG_CHU_NHIEM_TEN</t>
+          <t>Lê Bạch Mai</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>person_ten</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Đồng chủ nhiệm đề tài - chỉ tên</t>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DONG_CHU_NHIEM_HO_TEN</t>
+          <t>Nguyễn Thị Lâm</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>person_ho_ten</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Đồng chủ nhiệm đề tài - có học hàm/học vị</t>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>THU_KY_DE_TAI</t>
+          <t>Nguyễn Quang Dũng</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>person_ho_ten</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Thư ký đề tài</t>
+          <t>Bộ môn Dinh dưỡng - ĐH Y Hà Nội</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>THOI_GIAN_BAT_DAU</t>
+          <t>Hoàng Hà Linh</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>Thạc sĩ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>timeline_start</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mốc bắt đầu (MM/YYYY)</t>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>THOI_GIAN_KET_THUC</t>
+          <t>Trương Phan Hồng Hà</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>Thạc sĩ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>timeline_end</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Mốc kết thúc (MM/YYYY)</t>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DIA_DIEM_TRIEN_KHAI</t>
+          <t>Trần Quang Trung</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>PGS.TS.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>raw_or_placeholder</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>……………………………</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Địa điểm triển khai nghiên cứu</t>
+          <t>Hiệp hội Sữa Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Phạm Văn Hoàn</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ninh Thị Nhung</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trường Đại học Y Dược Thái Bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Trần Văn Ơn</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trường Đại học Dược Hà Nội</t>
         </is>
       </c>
     </row>
@@ -3969,313 +4018,340 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ten</t>
+          <t>token_name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>hoc_ham_hoc_vi</t>
+          <t>code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>don_vi</t>
+          <t>kind</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>dia_chi</t>
+          <t>param</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>sdt</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>cccd</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>mst</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>so_tk</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>ngan_hang</t>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Trương Hồng Sơn</t>
+          <t>TEN_DE_TAI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TS.BS.</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Viện trưởng - Viện Y học Ứng dụng VN</t>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Tên đề tài</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lưu Liên Hương</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thạc sĩ</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Năm thực hiện hồ sơ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lê Việt Anh</t>
+          <t>DON_VI_CHU_TRI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thạc sĩ</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cơ quan chủ trì</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lê Minh Khánh</t>
+          <t>DON_VI_DOI_TAC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bác sĩ</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phòng khám VIAM</t>
+          <t>raw_or_placeholder</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cơ quan phối hợp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nguyễn Công Khẩn</t>
+          <t>CHU_NHIEM_HO_TEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GS.TS.</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
+          <t>person_ho_ten</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Chủ nhiệm đề tài - có học hàm/học vị</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nguyễn Xuân Ninh</t>
+          <t>CHU_NHIEM_TEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>B01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>person_ten</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Chủ nhiệm đề tài - chỉ tên</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lê Bạch Mai</t>
+          <t>DONG_CHU_NHIEM_TEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+          <t>person_ten</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Đồng chủ nhiệm đề tài - chỉ tên</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Lâm</t>
+          <t>DONG_CHU_NHIEM_HO_TEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>B02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+          <t>person_ho_ten</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Đồng chủ nhiệm đề tài - có học hàm/học vị</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nguyễn Quang Dũng</t>
+          <t>THU_KY_DE_TAI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>B03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bộ môn Dinh dưỡng - ĐH Y Hà Nội</t>
+          <t>person_ho_ten</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Thư ký đề tài</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hoàng Hà Linh</t>
+          <t>THOI_GIAN_BAT_DAU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thạc sĩ</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
+          <t>timeline_start</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mốc bắt đầu (MM/YYYY)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Trương Phan Hồng Hà</t>
+          <t>THOI_GIAN_KET_THUC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thạc sĩ</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>timeline_end</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Mốc kết thúc (MM/YYYY)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trần Quang Trung</t>
+          <t>DIA_DIEM_TRIEN_KHAI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PGS.TS.</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hiệp hội Sữa Việt Nam</t>
+          <t>raw_or_placeholder</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>……………………………</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Địa điểm triển khai nghiên cứu</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Phạm Văn Hoàn</t>
+          <t>DAU_MOI_LIEN_HE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PGS.TS.</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Ninh Thị Nhung</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PGS.TS.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Trường Đại học Y Dược Thái Bình</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Trần Văn Ơn</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PGS.TS.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Trường Đại học Dược Hà Nội</t>
+          <t>raw_or_placeholder</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>……</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Đầu mối liên hệ (thư mời chuyên gia)</t>
         </is>
       </c>
     </row>

--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -8,9 +8,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Bánh ăn dặm VIAM 2027" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Mẫu trắng dự án mới" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Lists" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_NhanSu" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tokens" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_NhanSu" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tokens" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2037,7 +2036,7 @@
         </is>
       </c>
       <c r="F69">
-        <f>IF(ISBLANK(C69), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", IF(OR(ISBLANK(D69), ISBLANK(E69)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV Mặc định Đạo đức"))</f>
+        <f>IF(ISBLANK(C69), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", "✅ Đã khai chủ nhiệm đề tài - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -2053,7 +2052,7 @@
         </is>
       </c>
       <c r="F70">
-        <f>IF(ISBLANK(C70), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D70), ISBLANK(E70)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C70), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -2069,7 +2068,7 @@
         </is>
       </c>
       <c r="F71">
-        <f>IF(ISBLANK(C71), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D71), ISBLANK(E71)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C71), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -2100,7 +2099,7 @@
         </is>
       </c>
       <c r="F72">
-        <f>IF(ISBLANK(C72), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D72), ISBLANK(E72)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C72), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -2131,7 +2130,7 @@
         </is>
       </c>
       <c r="F73">
-        <f>IF(ISBLANK(C73), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D73), ISBLANK(E73)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C73), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -2162,7 +2161,7 @@
         </is>
       </c>
       <c r="F74">
-        <f>IF(ISBLANK(C74), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D74), ISBLANK(E74)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C74), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -2193,7 +2192,7 @@
         </is>
       </c>
       <c r="F75">
-        <f>IF(ISBLANK(C75), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D75), ISBLANK(E75)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C75), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -2224,7 +2223,7 @@
         </is>
       </c>
       <c r="F76">
-        <f>IF(ISBLANK(C76), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D76), ISBLANK(E76)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C76), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -2240,7 +2239,7 @@
         </is>
       </c>
       <c r="F77">
-        <f>IF(ISBLANK(C77), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D77), ISBLANK(E77)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C77), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -2256,7 +2255,7 @@
         </is>
       </c>
       <c r="F78">
-        <f>IF(ISBLANK(C78), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D78), ISBLANK(E78)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C78), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -3470,7 +3469,7 @@
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="3" t="n"/>
       <c r="F69">
-        <f>IF(ISBLANK(C69), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", IF(OR(ISBLANK(D69), ISBLANK(E69)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV Mặc định Đạo đức"))</f>
+        <f>IF(ISBLANK(C69), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", "✅ Đã khai chủ nhiệm đề tài - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -3486,7 +3485,7 @@
         </is>
       </c>
       <c r="F70">
-        <f>IF(ISBLANK(C70), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D70), ISBLANK(E70)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C70), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -3502,7 +3501,7 @@
         </is>
       </c>
       <c r="F71">
-        <f>IF(ISBLANK(C71), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D71), ISBLANK(E71)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C71), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -3518,7 +3517,7 @@
         </is>
       </c>
       <c r="F72">
-        <f>IF(ISBLANK(C72), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D72), ISBLANK(E72)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C72), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -3534,7 +3533,7 @@
         </is>
       </c>
       <c r="F73">
-        <f>IF(ISBLANK(C73), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D73), ISBLANK(E73)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C73), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -3550,7 +3549,7 @@
         </is>
       </c>
       <c r="F74">
-        <f>IF(ISBLANK(C74), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D74), ISBLANK(E74)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C74), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -3566,7 +3565,7 @@
         </is>
       </c>
       <c r="F75">
-        <f>IF(ISBLANK(C75), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D75), ISBLANK(E75)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C75), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -3582,7 +3581,7 @@
         </is>
       </c>
       <c r="F76">
-        <f>IF(ISBLANK(C76), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D76), ISBLANK(E76)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C76), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -3598,7 +3597,7 @@
         </is>
       </c>
       <c r="F77">
-        <f>IF(ISBLANK(C77), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D77), ISBLANK(E77)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C77), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -3614,7 +3613,7 @@
         </is>
       </c>
       <c r="F78">
-        <f>IF(ISBLANK(C78), "⚪ Tùy chọn (Trống)", IF(OR(ISBLANK(D78), ISBLANK(E78)), "❌ BÁO LỖI: CHƯA CÓ FILE CV TRONG THƯ MỤC KIỂM TRA (VUI LÒNG BỔ SUNG)", "✅ Đã kiểm tra &amp; liên kết CV"))</f>
+        <f>IF(ISBLANK(C78), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
       </c>
     </row>
@@ -3623,10 +3622,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="E68 E69 E70 E71 E72 E73 E74 E75 E76 E77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='_Lists'!$A$1:$A$6</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TVCT_ĐGHQ,TNLS"</formula1>
     </dataValidation>
@@ -3641,48 +3637,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Lý lịch khoa học - Trương Hồng Sơn.docx</t>
+          <t>ten</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>hoc_ham_hoc_vi</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>don_vi</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>dia_chi</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sdt</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>cccd</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>mst</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>so_tk</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ngan_hang</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TM-Gs. Nguyen Cong Khan.pdf</t>
+          <t>Trương Hồng Sơn</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TS.BS.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Viện trưởng - Viện Y học Ứng dụng VN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TM-PGs. Hoang Thi Thanh.pdf</t>
+          <t>Lưu Liên Hương</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TM-PGs. Nguyen Quang Dung.pdf</t>
+          <t>Lê Việt Anh</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TM-PGs. Tran Quang Trung.pdf</t>
+          <t>Lê Minh Khánh</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bác sĩ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Phòng khám VIAM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TM-Ts. Nguyen Hung Long.pdf</t>
+          <t>Nguyễn Công Khẩn</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GS.TS.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nguyễn Xuân Ninh</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lê Bạch Mai</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Lâm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Nguyễn Quang Dũng</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bộ môn Dinh dưỡng - ĐH Y Hà Nội</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hoàng Hà Linh</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Trung tâm NCKH - Viện VIAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Trương Phan Hồng Hà</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Trần Quang Trung</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hiệp hội Sữa Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Phạm Văn Hoàn</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ninh Thị Nhung</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trường Đại học Y Dược Thái Bình</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Trần Văn Ơn</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trường Đại học Dược Hà Nội</t>
         </is>
       </c>
     </row>
@@ -3697,327 +3958,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ten</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>hoc_ham_hoc_vi</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>don_vi</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>dia_chi</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>sdt</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>cccd</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>mst</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>so_tk</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>ngan_hang</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Trương Hồng Sơn</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TS.BS.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Viện trưởng - Viện Y học Ứng dụng VN</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Lưu Liên Hương</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Lê Việt Anh</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Lê Minh Khánh</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Bác sĩ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Phòng khám VIAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Nguyễn Công Khẩn</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>GS.TS.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Nguyễn Xuân Ninh</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PGS.TS.BS.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Lê Bạch Mai</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PGS.TS.BS.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Lâm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PGS.TS.BS.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Nguyễn Quang Dũng</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PGS.TS.BS.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bộ môn Dinh dưỡng - ĐH Y Hà Nội</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Hoàng Hà Linh</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Trương Phan Hồng Hà</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Trần Quang Trung</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PGS.TS.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Hiệp hội Sữa Việt Nam</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Phạm Văn Hoàn</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PGS.TS.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Ninh Thị Nhung</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PGS.TS.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Trường Đại học Y Dược Thái Bình</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Trần Văn Ơn</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PGS.TS.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Trường Đại học Dược Hà Nội</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -4064,7 +4004,6 @@
           <t>raw</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Tên đề tài</t>
@@ -4087,7 +4026,6 @@
           <t>raw</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Năm thực hiện hồ sơ</t>
@@ -4110,7 +4048,6 @@
           <t>raw</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Cơ quan chủ trì</t>
@@ -4133,7 +4070,6 @@
           <t>raw_or_placeholder</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Cơ quan phối hợp</t>
@@ -4156,7 +4092,6 @@
           <t>person_ho_ten</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Chủ nhiệm đề tài - có học hàm/học vị</t>
@@ -4179,7 +4114,6 @@
           <t>person_ten</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Chủ nhiệm đề tài - chỉ tên</t>
@@ -4202,7 +4136,6 @@
           <t>person_ten</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Đồng chủ nhiệm đề tài - chỉ tên</t>
@@ -4225,7 +4158,6 @@
           <t>person_ho_ten</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Đồng chủ nhiệm đề tài - có học hàm/học vị</t>
@@ -4248,7 +4180,6 @@
           <t>person_ho_ten</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Thư ký đề tài</t>
@@ -4271,7 +4202,6 @@
           <t>timeline_start</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Mốc bắt đầu (MM/YYYY)</t>
@@ -4294,7 +4224,6 @@
           <t>timeline_end</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Mốc kết thúc (MM/YYYY)</t>

--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -9,7 +9,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Bánh ăn dặm VIAM 2027" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Mẫu trắng dự án mới" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_NhanSu" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tokens" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2083,21 +2082,6 @@
           <t>Hồ sơ Chuyên gia / Thành viên 4 (Tùy chọn)</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Nguyễn Công Khẩn</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Chuyên gia hội đồng</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>TM-Gs. Nguyen Cong Khan.pdf</t>
-        </is>
-      </c>
       <c r="F72">
         <f>IF(ISBLANK(C72), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
@@ -2114,21 +2098,6 @@
           <t>Hồ sơ Chuyên gia / Thành viên 5 (Tùy chọn)</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Hoàng Thị Thanh</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Chuyên gia hội đồng</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>TM-PGs. Hoang Thi Thanh.pdf</t>
-        </is>
-      </c>
       <c r="F73">
         <f>IF(ISBLANK(C73), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
@@ -2145,21 +2114,6 @@
           <t>Hồ sơ Chuyên gia / Thành viên 6 (Tùy chọn)</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Nguyễn Quang Dũng</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Chuyên gia hội đồng</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>TM-PGs. Nguyen Quang Dung.pdf</t>
-        </is>
-      </c>
       <c r="F74">
         <f>IF(ISBLANK(C74), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
@@ -2176,21 +2130,6 @@
           <t>Hồ sơ Chuyên gia / Thành viên 7 (Tùy chọn)</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Trần Quang Trung</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Chuyên gia hội đồng</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>TM-PGs. Tran Quang Trung.pdf</t>
-        </is>
-      </c>
       <c r="F75">
         <f>IF(ISBLANK(C75), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
         <v/>
@@ -2205,21 +2144,6 @@
       <c r="B76" t="inlineStr">
         <is>
           <t>Hồ sơ Chuyên gia / Thành viên 8 (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Nguyễn Hùng Long</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Chuyên gia hội đồng</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>TM-Ts. Nguyen Hung Long.pdf</t>
         </is>
       </c>
       <c r="F76">
@@ -3950,341 +3874,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>token_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>kind</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>param</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TEN_DE_TAI</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Tên đề tài</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NAM</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Năm thực hiện hồ sơ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DON_VI_CHU_TRI</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Cơ quan chủ trì</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DON_VI_DOI_TAC</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>raw_or_placeholder</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Cơ quan phối hợp</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CHU_NHIEM_HO_TEN</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>person_ho_ten</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Chủ nhiệm đề tài - có học hàm/học vị</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CHU_NHIEM_TEN</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>person_ten</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Chủ nhiệm đề tài - chỉ tên</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DONG_CHU_NHIEM_TEN</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>B02</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>person_ten</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Đồng chủ nhiệm đề tài - chỉ tên</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DONG_CHU_NHIEM_HO_TEN</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>B02</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>person_ho_ten</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Đồng chủ nhiệm đề tài - có học hàm/học vị</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>THU_KY_DE_TAI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>B03</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>person_ho_ten</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Thư ký đề tài</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>THOI_GIAN_BAT_DAU</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>A05</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>timeline_start</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mốc bắt đầu (MM/YYYY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>THOI_GIAN_KET_THUC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>A05</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>timeline_end</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Mốc kết thúc (MM/YYYY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DIA_DIEM_TRIEN_KHAI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>A07</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>raw_or_placeholder</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>……………………………</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Địa điểm triển khai nghiên cứu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DAU_MOI_LIEN_HE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>A08</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>raw_or_placeholder</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>……</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Đầu mối liên hệ (thư mời chuyên gia)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Bánh ăn dặm VIAM 2027" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Mẫu trắng dự án mới" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_NhanSu" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tokens" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -17,8 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <name val="Arial"/>
       <family val="2"/>
@@ -61,8 +64,18 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F497D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -93,8 +106,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F1"/>
+        <bgColor rgb="00DCE6F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -102,11 +121,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -114,6 +147,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -535,6 +571,7 @@
         <v/>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -2183,11 +2220,423 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>SEC_G</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>PHẦN G: SỐ VĂN BẢN, NGÀY KÝ, BỐI CẢNH &amp; LỊCH HỌP (TÙY CHỌN - ĐỂ TRỐNG SẼ GIỮ NGUYÊN DẤU CHẤM LỬNG)</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="7" t="n"/>
+      <c r="E79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>G01</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Bối cảnh / lý do triển khai đề tài (Điền nội dung hoặc để trống)</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{BOI_CANH_DU_AN}}</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>G02</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Địa điểm họp Hội đồng (Tùy chọn - Để trống dùng địa chỉ Viện)</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{DIA_DIEM_HOP}}</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>G03</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Thời gian họp chung (giờ, ngày tháng - Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{THOI_GIAN_HOP}}</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>G04</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Số công văn mời chuyên gia (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_CONG_VAN}}</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>G05</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký công văn mời chuyên gia (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>G06</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Số Quyết định giao đề tài - Mẫu 00 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_QD_GIAO_DE_TAI}}</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>G07</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ giao đề tài (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>G08</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Đạo đức - Mẫu 01 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="n"/>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_QD_TLHD_DAO_DUC}}</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>G09</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Đạo đức (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Khoa học - Mẫu 05 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="n"/>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_QD_TLHD_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Khoa học (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Nghiệm thu - Mẫu 9 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_QD_TLHD_NGHIEM_THU}}</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Nghiệm thu (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ Phê duyệt đề tài - Mẫu 08 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_QD_PHE_DUYET}}</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>G15</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ Phê duyệt đề tài (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>G16</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ Công nhận kết quả - Mẫu 12 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="n"/>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_QD_CONG_NHAN}}</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>G17</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ Công nhận kết quả (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>G18</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Đạo đức - Mẫu 02, 03 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="n"/>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>G19</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Khoa học - Mẫu 06, 07 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>G20</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Nghiệm thu - Mẫu 10, 11 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="n"/>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='_NhanSu'!$A$2:$A$16</formula1>
+    </dataValidation>
+    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Nghiên cứu can thiệp,Nghiên cứu quan sát,Thử nghiệm lâm sàng,Đánh giá hiệu quả công thức,Khác"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"GS.TS.,PGS.TS.,TS.,ThS.,BS.CKII,BS.CKI,BS.,CN.,DS."</formula1>
+    </dataValidation>
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24 A25 A26 A27 A28 A29 A30 A31 A32 A33 A34 A36 A37 A38 A39 A40 A41 A42 A43 A44 A45 A47 A48 A49 A50 A51 A52 A53 A54 A55 A56 A58 A59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='_Tokens'!$A$2:$A$38</formula1>
+    </dataValidation>
+    <dataValidation sqref="C84 C86 C88 C90 C92 C94 C96 C97 C98 C99" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Sai định dạng ngày" error="Vui lòng nhập ngày hợp lệ (VD: 15/03/2027 hoặc chọn từ lịch)" promptTitle="Nhập ngày" prompt="Định dạng ngày: DD/MM/YYYY" type="date" operator="greaterThanOrEqual">
+      <formula1>DATE(1900,1,1)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2198,7 +2647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2222,6 +2671,7 @@
         <v/>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -2450,8 +2900,8 @@
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr"/>
       <c r="F15">
         <f>IF(ISBLANK(C15), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -2740,11 +3190,6 @@
           <t>Nghiên cứu viên 16</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>(Để trống tên theo quy định)</t>
-        </is>
-      </c>
       <c r="F33">
         <f>IF(ISBLANK(C33), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
@@ -2759,11 +3204,6 @@
       <c r="B34" t="inlineStr">
         <is>
           <t>Nghiên cứu viên 17</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>(Để trống tên theo quy định)</t>
         </is>
       </c>
       <c r="F34">
@@ -2799,8 +3239,8 @@
         </is>
       </c>
       <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
       <c r="F36">
         <f>IF(ISBLANK(C36), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -2818,8 +3258,8 @@
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
+      <c r="D37" s="3" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
       <c r="F37">
         <f>IF(ISBLANK(C37), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -2837,8 +3277,8 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
+      <c r="D38" s="3" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr"/>
       <c r="F38">
         <f>IF(ISBLANK(C38), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -2856,8 +3296,8 @@
         </is>
       </c>
       <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
       <c r="F39">
         <f>IF(ISBLANK(C39), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -2875,8 +3315,8 @@
         </is>
       </c>
       <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr"/>
       <c r="F40">
         <f>IF(ISBLANK(C40), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -2942,8 +3382,8 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
       <c r="F44">
         <f>IF(ISBLANK(C44), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -2961,8 +3401,8 @@
         </is>
       </c>
       <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="3" t="inlineStr"/>
       <c r="F45">
         <f>IF(ISBLANK(C45), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -2996,8 +3436,8 @@
         </is>
       </c>
       <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="3" t="inlineStr"/>
       <c r="F47">
         <f>IF(ISBLANK(C47), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3015,8 +3455,8 @@
         </is>
       </c>
       <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="n"/>
+      <c r="D48" s="3" t="inlineStr"/>
+      <c r="E48" s="3" t="inlineStr"/>
       <c r="F48">
         <f>IF(ISBLANK(C48), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3034,8 +3474,8 @@
         </is>
       </c>
       <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
+      <c r="D49" s="3" t="inlineStr"/>
+      <c r="E49" s="3" t="inlineStr"/>
       <c r="F49">
         <f>IF(ISBLANK(C49), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3053,8 +3493,8 @@
         </is>
       </c>
       <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="n"/>
+      <c r="D50" s="3" t="inlineStr"/>
+      <c r="E50" s="3" t="inlineStr"/>
       <c r="F50">
         <f>IF(ISBLANK(C50), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3072,8 +3512,8 @@
         </is>
       </c>
       <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
+      <c r="D51" s="3" t="inlineStr"/>
+      <c r="E51" s="3" t="inlineStr"/>
       <c r="F51">
         <f>IF(ISBLANK(C51), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3139,8 +3579,8 @@
         </is>
       </c>
       <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
-      <c r="E55" s="3" t="n"/>
+      <c r="D55" s="3" t="inlineStr"/>
+      <c r="E55" s="3" t="inlineStr"/>
       <c r="F55">
         <f>IF(ISBLANK(C55), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3158,8 +3598,8 @@
         </is>
       </c>
       <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="3" t="n"/>
+      <c r="D56" s="3" t="inlineStr"/>
+      <c r="E56" s="3" t="inlineStr"/>
       <c r="F56">
         <f>IF(ISBLANK(C56), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3193,8 +3633,8 @@
         </is>
       </c>
       <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="3" t="n"/>
+      <c r="D58" s="3" t="inlineStr"/>
+      <c r="E58" s="3" t="inlineStr"/>
       <c r="F58">
         <f>IF(ISBLANK(C58), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3212,8 +3652,8 @@
         </is>
       </c>
       <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="3" t="n"/>
+      <c r="D59" s="3" t="inlineStr"/>
+      <c r="E59" s="3" t="inlineStr"/>
       <c r="F59">
         <f>IF(ISBLANK(C59), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3231,8 +3671,8 @@
         </is>
       </c>
       <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="n"/>
+      <c r="D60" s="3" t="inlineStr"/>
+      <c r="E60" s="3" t="inlineStr"/>
       <c r="F60">
         <f>IF(ISBLANK(C60), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3250,8 +3690,8 @@
         </is>
       </c>
       <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
+      <c r="D61" s="3" t="inlineStr"/>
+      <c r="E61" s="3" t="inlineStr"/>
       <c r="F61">
         <f>IF(ISBLANK(C61), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3269,8 +3709,8 @@
         </is>
       </c>
       <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
+      <c r="D62" s="3" t="inlineStr"/>
+      <c r="E62" s="3" t="inlineStr"/>
       <c r="F62">
         <f>IF(ISBLANK(C62), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3336,8 +3776,8 @@
         </is>
       </c>
       <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="n"/>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="3" t="inlineStr"/>
       <c r="F66">
         <f>IF(ISBLANK(C66), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3355,8 +3795,8 @@
         </is>
       </c>
       <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="3" t="inlineStr"/>
       <c r="F67">
         <f>IF(ISBLANK(C67), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
@@ -3541,14 +3981,421 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>SEC_G</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>PHẦN G: SỐ VĂN BẢN, NGÀY KÝ, BỐI CẢNH &amp; LỊCH HỌP (TÙY CHỌN - ĐỂ TRỐNG SẼ GIỮ NGUYÊN DẤU CHẤM LỬNG)</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="7" t="n"/>
+      <c r="E79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>G01</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Bối cảnh / lý do triển khai đề tài (Điền nội dung hoặc để trống)</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{BOI_CANH_DU_AN}}</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>G02</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Địa điểm họp Hội đồng (Tùy chọn - Để trống dùng địa chỉ Viện)</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="n"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{DIA_DIEM_HOP}}</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>G03</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Thời gian họp chung (giờ, ngày tháng - Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{THOI_GIAN_HOP}}</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>G04</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Số công văn mời chuyên gia (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_CONG_VAN}}</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>G05</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký công văn mời chuyên gia (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>G06</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Số Quyết định giao đề tài - Mẫu 00 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_QD_GIAO_DE_TAI}}</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>G07</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ giao đề tài (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>G08</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Đạo đức - Mẫu 01 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="n"/>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_QD_TLHD_DAO_DUC}}</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>G09</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Đạo đức (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Khoa học - Mẫu 05 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="n"/>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_QD_TLHD_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Khoa học (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Nghiệm thu - Mẫu 9 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_QD_TLHD_NGHIEM_THU}}</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Nghiệm thu (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ Phê duyệt đề tài - Mẫu 08 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_QD_PHE_DUYET}}</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>G15</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ Phê duyệt đề tài (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>G16</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ Công nhận kết quả - Mẫu 12 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="n"/>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Token: {{SO_QD_CONG_NHAN}}</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>G17</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ Công nhận kết quả (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>G18</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Đạo đức - Mẫu 02, 03 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="n"/>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>G19</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Khoa học - Mẫu 06, 07 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>G20</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Nghiệm thu - Mẫu 10, 11 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="n"/>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Định dạng: DD/MM/YYYY</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="5">
+    <dataValidation sqref="C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='_NhanSu'!$A$2:$A$16</formula1>
+    </dataValidation>
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TVCT_ĐGHQ,TNLS"</formula1>
+      <formula1>"Nghiên cứu can thiệp,Nghiên cứu quan sát,Thử nghiệm lâm sàng,Đánh giá hiệu quả công thức,Khác"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"GS.TS.,PGS.TS.,TS.,ThS.,BS.CKII,BS.CKI,BS.,CN.,DS."</formula1>
+    </dataValidation>
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24 A25 A26 A27 A28 A29 A30 A31 A32 A33 A34 A36 A37 A38 A39 A40 A41 A42 A43 A44 A45 A47 A48 A49 A50 A51 A52 A53 A54 A55 A56 A58 A59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='_Tokens'!$A$2:$A$38</formula1>
+    </dataValidation>
+    <dataValidation sqref="C84 C86 C88 C90 C92 C94 C96 C97 C98 C99" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Sai định dạng ngày" error="Vui lòng nhập ngày hợp lệ (VD: 15/03/2027 hoặc chọn từ lịch)" promptTitle="Nhập ngày" prompt="Định dạng ngày: DD/MM/YYYY" type="date" operator="greaterThanOrEqual">
+      <formula1>DATE(1900,1,1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3874,4 +4721,664 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>TOKEN_TAG</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>MÃ_MỤC</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MÔ_TẢ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>{{TEN_DE_TAI}}</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tên đề tài nghiên cứu</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>{{NAM}}</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Năm thực hiện hồ sơ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>{{DON_VI_CHU_TRI}}</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Cơ quan chủ trì</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>{{DON_VI_DOI_TAC}}</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cơ quan phối hợp (tùy chọn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>{{THOI_GIAN_BAT_DAU}}</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mốc thời gian bắt đầu (MM/YYYY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>{{THOI_GIAN_KET_THUC}}</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mốc thời gian kết thúc (MM/YYYY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>{{DIA_DIEM_TRIEN_KHAI}}</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Địa điểm triển khai nghiên cứu</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>{{DAU_MOI_LIEN_HE}}</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Đầu mối liên hệ thư mời</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>{{CHU_NHIEM_HO_TEN}}</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Họ tên Chủ nhiệm đề tài</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>{{CHU_NHIEM_TEN}}</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tên riêng Chủ nhiệm đề tài</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>{{CHU_NHIEM_DON_VI}}</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Đơn vị công tác Chủ nhiệm đề tài</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>{{DONG_CHU_NHIEM_HO_TEN}}</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B02</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Họ tên Đồng chủ nhiệm đề tài</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>{{THU_KY_DE_TAI}}</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Họ tên Thư ký đề tài</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>{{DANH_SACH_NGHIEN_CUU_VIEN}}</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B04-B20</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Danh sách nghiên cứu viên</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>{{CHU_TICH_HD_DAO_DUC}}</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chủ tịch HĐ Đạo đức</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>{{CHU_TICH_HD_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chủ tịch HĐ Khoa học</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>{{CHU_TICH_HD_NGHIEM_THU}}</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chủ tịch HĐ Nghiệm thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>{{BOI_CANH_DU_AN}}</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>G01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bối cảnh / lý do triển khai đề tài</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>{{DIA_DIEM_HOP}}</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>G02</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Địa điểm họp Hội đồng</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>{{THOI_GIAN_HOP}}</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>G03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Thời gian họp Hội đồng (giờ, ngày tháng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>{{SO_CONG_VAN}}</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>G04</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Số công văn mời chuyên gia</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>{{NGAY_CONG_VAN}}</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>G05</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ngày ký công văn mời chuyên gia</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>{{SO_QD_GIAO_DE_TAI}}</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>G06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Số Quyết định giao đề tài (00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_GIAO_DE_TAI}}</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>G07</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ giao đề tài</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>{{SO_QD_TLHD_DAO_DUC}}</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>G08</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Đạo đức (01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_TLHD_DAO_DUC}}</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>G09</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Đạo đức</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>{{SO_QD_TLHD_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Khoa học (05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_TLHD_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Khoa học</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>{{SO_QD_TLHD_PHE_DUYET}}</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Số QĐ Phê duyệt đề tài (08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_PHE_DUYET}}</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>G15</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ Phê duyệt đề tài</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>{{SO_QD_TLHD_NGHIEM_THU}}</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Nghiệm thu (9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_TLHD_NGHIEM_THU}}</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Nghiệm thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>{{SO_QD_CONG_NHAN}}</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>G16</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Số QĐ Công nhận kết quả (12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_CONG_NHAN}}</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>G17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ Công nhận kết quả</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>{{NGAY_HOP_DAO_DUC}}</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>G18</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Đạo đức (02, 03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>{{NGAY_HOP_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>G19</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Khoa học (06, 07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>{{NGAY_HOP_NGHIEM_THU}}</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>G20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Nghiệm thu (10, 11)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Form checklist hồ sơ dự án.xlsx
+++ b/Form checklist hồ sơ dự án.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đề tài - Mẫu trắng dự án mới" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_NhanSu" sheetId="3" state="hidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tokens" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_BoHoSo" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -547,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -567,11 +568,27 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="5">
-        <f>IF(COUNTIF(F6:F150, "*BÁO LỖI*")&gt;0, "⚠️ BÁO LỖI: PHÁT HIỆN CHƯA CÓ FILE CV CHUYÊN GIA HOẶC THIẾU THÔNG TIN BẮT BUỘC - VUI LÒNG BỔ SUNG CÁC Ô MÀU ĐỎ DƯỚI ĐÂY", "🎉 HOÀN THÀNH 100%: TẤT CẢ THÔNG TIN &amp; FILE CV CHUYÊN GIA ĐÃ ĐẦY ĐỦ - SẴN SÀNG CHẠY RA BỘ HỒ SƠ HOÀN CHỈNH")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3"/>
+        <f>IF(COUNTIF(F6:F150, "*BÁO LỖI*")&gt;0, "⚠️ BÁO LỖI: PHÁT HIỆN THIẾU THÔNG TIN BẮT BUỘC CỦA BỘ HỒ SƠ ĐÃ CHỌN - VUI LÒNG BỔ SUNG CÁC Ô MÀU ĐỎ DƯỚI ĐÂY", "🎉 HOÀN THÀNH 100%: TẤT CẢ THÔNG TIN BẮT BUỘC CHO BỘ HỒ SƠ ĐÃ CHỌN ĐÃ ĐẦY ĐỦ - SẴN SÀNG CHẠY RA BỘ HỒ SƠ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BO_HO_SO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CHỌN BỘ HỒ SƠ (A: NCKH &amp; Đánh giá công thức / B: Thử nghiệm lâm sàng / C: Quan sát dịch tễ / D: Chuyển giao CN)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -612,7 +629,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PHẦN A: THÔNG TIN CHUNG DỰ ÁN &amp; ĐỀ TÀI</t>
+          <t>PHẦN A: THÔNG TIN CHUNG DỰ ÁN &amp; ĐỀ TÀI (BẮT BUỘC TẤT CẢ CÁC BỘ)</t>
         </is>
       </c>
       <c r="C5" s="2" t="n"/>
@@ -623,7 +640,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>{{TEN_DE_TAI}}</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -646,7 +663,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>{{LOAI_HINH_NC}}</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -669,7 +686,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>{{NAM}}</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -690,7 +707,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>{{DON_VI_CHU_TRI}}</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -713,7 +730,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>{{THOI_GIAN_BAT_DAU}}</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -736,7 +753,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>{{DON_VI_DOI_TAC}}</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -755,7 +772,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>{{DIA_DIEM_TRIEN_KHAI}}</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -774,7 +791,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>{{DAU_MOI_LIEN_HE}}</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -791,61 +808,61 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>SEC_B</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>PHẦN B: BAN CHỦ NHIỆM &amp; NGHIÊN CỨU VIÊN ĐỀ TÀI (TỐI ĐA 20 NGƯỜI)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>{{BOI_CANH_DU_AN}}</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Bối cảnh / lý do triển khai đề tài (Điền nội dung hoặc để trống)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Nghiên cứu về dinh dưỡng trẻ em</t>
+        </is>
+      </c>
+      <c r="F14">
+        <f>IF(ISBLANK(C14), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>B01</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Chủ nhiệm đề tài (CNĐT - Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Trương Hồng Sơn</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>TS.BS.</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Viện trưởng - Viện Y học Ứng dụng VN</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>{{DIA_DIEM_HOP}}</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Địa điểm họp Hội đồng (Tùy chọn - Để trống dùng địa chỉ Viện)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Viện Y học ứng dụng Việt Nam</t>
         </is>
       </c>
       <c r="F15">
-        <f>IF(ISBLANK(C15), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C15), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>B02</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Đồng Chủ nhiệm đề tài (Tùy chọn)</t>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>{{THOI_GIAN_HOP}}</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Thời gian họp chung (giờ, ngày tháng - Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>09:00, 15/10/2027</t>
         </is>
       </c>
       <c r="F16">
@@ -854,155 +871,129 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>B03</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Thư ký Đề tài (Khác Thư ký HĐ - Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Lưu Liên Hương</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
-        </is>
-      </c>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>{{SO_CONG_VAN}}</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Số công văn mời chuyên gia (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
       <c r="F17">
         <f>IF(ISBLANK(C17), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>B04</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Nghiên cứu viên 1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Lê Việt Anh</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
-        </is>
-      </c>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>{{NGAY_CONG_VAN}}</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký công văn mời chuyên gia (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n"/>
       <c r="F18">
         <f>IF(ISBLANK(C18), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>B05</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Nghiên cứu viên 2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Lê Minh Khánh</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Bác sĩ</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Phòng khám VIAM</t>
-        </is>
-      </c>
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>{{SO_QD_GIAO_DE_TAI}}</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Số Quyết định giao đề tài - Mẫu 00 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
       <c r="F19">
         <f>IF(ISBLANK(C19), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>B06</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Nghiên cứu viên 3</t>
-        </is>
-      </c>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_GIAO_DE_TAI}}</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ giao đề tài (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
       <c r="F20">
         <f>IF(ISBLANK(C20), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>B07</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Nghiên cứu viên 4</t>
-        </is>
-      </c>
-      <c r="F21">
-        <f>IF(ISBLANK(C21), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SEC_B</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>PHẦN B: BAN CHỦ NHIỆM &amp; NGHIÊN CỨU VIÊN ĐỀ TÀI (CHỦ NHIỆM BẮT BUỘC)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B08</t>
+          <t>{{CHU_NHIEM_HO_TEN}}</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 5</t>
+          <t>Chủ nhiệm đề tài (CNĐT - Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Trương Hồng Sơn</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>TS.BS.</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Viện trưởng - Viện Y học Ứng dụng VN</t>
         </is>
       </c>
       <c r="F22">
-        <f>IF(ISBLANK(C22), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C22), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B09</t>
+          <t>{{DONG_CHU_NHIEM_HO_TEN}}</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 6</t>
+          <t>Đồng Chủ nhiệm đề tài (Tùy chọn)</t>
         </is>
       </c>
       <c r="F23">
@@ -1013,12 +1004,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B10</t>
+          <t>{{THU_KY_DE_TAI}}</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 7</t>
+          <t>Thư ký Đề tài (Khác Thư ký HĐ - Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lưu Liên Hương</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
       <c r="F24">
@@ -1029,12 +1035,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>{{DANH_SACH_NGHIEN_CUU_VIEN}}</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 8</t>
+          <t>Nghiên cứu viên 1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Lê Việt Anh</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
       <c r="F25">
@@ -1045,12 +1066,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 9</t>
+          <t>Nghiên cứu viên 2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Lê Minh Khánh</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bác sĩ</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Phòng khám VIAM</t>
         </is>
       </c>
       <c r="F26">
@@ -1061,12 +1097,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B13</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 10</t>
+          <t>Nghiên cứu viên 3</t>
         </is>
       </c>
       <c r="F27">
@@ -1077,12 +1113,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>B07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 11</t>
+          <t>Nghiên cứu viên 4</t>
         </is>
       </c>
       <c r="F28">
@@ -1093,12 +1129,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B15</t>
+          <t>B08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 12</t>
+          <t>Nghiên cứu viên 5</t>
         </is>
       </c>
       <c r="F29">
@@ -1109,12 +1145,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B16</t>
+          <t>B09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 13</t>
+          <t>Nghiên cứu viên 6</t>
         </is>
       </c>
       <c r="F30">
@@ -1125,12 +1161,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B17</t>
+          <t>B10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 14</t>
+          <t>Nghiên cứu viên 7</t>
         </is>
       </c>
       <c r="F31">
@@ -1141,12 +1177,12 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B18</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 15</t>
+          <t>Nghiên cứu viên 8</t>
         </is>
       </c>
       <c r="F32">
@@ -1157,12 +1193,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B19</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 16</t>
+          <t>Nghiên cứu viên 9</t>
         </is>
       </c>
       <c r="F33">
@@ -1173,12 +1209,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B20</t>
+          <t>B13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nghiên cứu viên 17</t>
+          <t>Nghiên cứu viên 10</t>
         </is>
       </c>
       <c r="F34">
@@ -1187,185 +1223,110 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>SEC_C</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>PHẦN C: HỘI ĐỒNG ĐẠO ĐỨC TRONG NGHIÊN CỨU (HĐ 01 - 7 THÀNH VIÊN BẮT BUỘC)</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nghiên cứu viên 11</t>
+        </is>
+      </c>
+      <c r="F35">
+        <f>IF(ISBLANK(C35), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>B15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chủ tịch HĐ Đạo đức (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Nguyễn Công Khẩn</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>GS.TS.</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
+          <t>Nghiên cứu viên 12</t>
         </is>
       </c>
       <c r="F36">
-        <f>IF(ISBLANK(C36), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C36), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>B16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Nguyễn Xuân Ninh</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>PGS.TS.BS.</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Nghiên cứu viên 13</t>
         </is>
       </c>
       <c r="F37">
-        <f>IF(ISBLANK(C37), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C37), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>B17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Lê Bạch Mai</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>PGS.TS.BS.</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+          <t>Nghiên cứu viên 14</t>
         </is>
       </c>
       <c r="F38">
-        <f>IF(ISBLANK(C38), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C38), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>B18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Lâm</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>PGS.TS.BS.</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+          <t>Nghiên cứu viên 15</t>
         </is>
       </c>
       <c r="F39">
-        <f>IF(ISBLANK(C39), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C39), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>B19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 2 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Nguyễn Quang Dũng</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>PGS.TS.BS.</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Bộ môn Dinh dưỡng - ĐH Y Hà Nội</t>
+          <t>Nghiên cứu viên 16</t>
         </is>
       </c>
       <c r="F40">
-        <f>IF(ISBLANK(C40), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C40), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>B20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
+          <t>Nghiên cứu viên 17</t>
         </is>
       </c>
       <c r="F41">
@@ -1374,415 +1335,401 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>C07</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Ủy viên HĐ Đạo đức 3 (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="F42">
-        <f>IF(ISBLANK(C42), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SEC_C</t>
+        </is>
+      </c>
+      <c r="B42" s="2">
+        <f>"PHẦN C: HỘI ĐỒNG ĐẠO ĐỨC TRONG NGHIÊN CỨU " &amp; IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), "🟢 [BẮT BUỘC - ĐANG ÁP DỤNG]", "⚪ [KHÔNG ÁP DỤNG CHO BỘ NÀY]")</f>
+        <v/>
+      </c>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C08</t>
+          <t>{{CHU_TICH_HD_DAO_DUC}}</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đạo đức 4 (Tùy chọn)</t>
+          <t>Chủ tịch HĐ Đạo đức (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Công Khẩn</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>GS.TS.</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
         </is>
       </c>
       <c r="F43">
-        <f>IF(ISBLANK(C43), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C43), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C09</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đạo đức 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Hoàng Hà Linh</t>
+          <t>Nguyễn Xuân Ninh</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Thạc sĩ</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
         </is>
       </c>
       <c r="F44">
-        <f>IF(ISBLANK(C44), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C44), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Đạo đức 2 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Trương Phan Hồng Hà</t>
+          <t>Lê Bạch Mai</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Thạc sĩ</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
         </is>
       </c>
       <c r="F45">
-        <f>IF(ISBLANK(C45), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C45), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>SEC_D</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>PHẦN D: HỘI ĐỒNG KHOA HỌC XÉT DUYỆT ĐỀ CƯƠNG (HĐ 02 - 7 THÀNH VIÊN BẮT BUỘC)</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ủy viên HĐ Đạo đức 1 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Lâm</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+        </is>
+      </c>
+      <c r="F46">
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C46), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>C05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chủ tịch HĐ Đề cương (Bắt buộc)</t>
+          <t>Ủy viên HĐ Đạo đức 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Công Khẩn</t>
+          <t>Nguyễn Quang Dũng</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>GS.TS.</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
+          <t>Bộ môn Dinh dưỡng - ĐH Y Hà Nội</t>
         </is>
       </c>
       <c r="F47">
-        <f>IF(ISBLANK(C47), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C47), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D02</t>
+          <t>C06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Nguyễn Xuân Ninh</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>PGS.TS.BS.</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F48">
-        <f>IF(ISBLANK(C48), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C48), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D03</t>
+          <t>C07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Trần Quang Trung</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>PGS.TS.</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Hiệp hội Sữa Việt Nam</t>
+          <t>Ủy viên HĐ Đạo đức 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F49">
-        <f>IF(ISBLANK(C49), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C49), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>D04</t>
+          <t>C08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Lê Bạch Mai</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>PGS.TS.BS.</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+          <t>Ủy viên HĐ Đạo đức 4 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F50">
-        <f>IF(ISBLANK(C50), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C50), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>D05</t>
+          <t>C09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Đề cương 2 (Bắt buộc)</t>
+          <t>Thư ký HĐ Đạo đức 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Lâm</t>
+          <t>Hoàng Hà Linh</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>Thạc sĩ</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
       <c r="F51">
-        <f>IF(ISBLANK(C51), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C51), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>C10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
+          <t>Thư ký HĐ Đạo đức 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Trương Phan Hồng Hà</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
         </is>
       </c>
       <c r="F52">
-        <f>IF(ISBLANK(C52), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C52), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>D07</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Ủy viên HĐ Đề cương 3 (Tùy chọn)</t>
-        </is>
-      </c>
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>{{SO_QD_TLHD_DAO_DUC}}</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Đạo đức - Mẫu 01 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="n"/>
       <c r="F53">
         <f>IF(ISBLANK(C53), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Ủy viên HĐ Đề cương 4 (Tùy chọn)</t>
-        </is>
-      </c>
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_TLHD_DAO_DUC}}</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Đạo đức (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n"/>
       <c r="F54">
         <f>IF(ISBLANK(C54), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>D09</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Thư ký HĐ Đề cương 1 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Hoàng Hà Linh</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>Trung tâm NCKH - Viện VIAM</t>
-        </is>
-      </c>
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>{{NGAY_HOP_DAO_DUC}}</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Đạo đức - Mẫu 02, 03 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n"/>
       <c r="F55">
-        <f>IF(ISBLANK(C55), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C55), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>D10</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Thư ký HĐ Đề cương 2 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>Trương Phan Hồng Hà</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
-        </is>
-      </c>
-      <c r="F56">
-        <f>IF(ISBLANK(C56), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
-        <v/>
-      </c>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>SEC_D</t>
+        </is>
+      </c>
+      <c r="B56" s="2">
+        <f>"PHẦN D: HỘI ĐỒNG KHOA HỌC XÉT DUYỆT ĐỀ CƯƠNG " &amp; IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), "🟢 [BẮT BUỘC - ĐANG ÁP DỤNG]", "⚪ [KHÔNG ÁP DỤNG CHO BỘ NÀY]")</f>
+        <v/>
+      </c>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>SEC_E</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>PHẦN E: HỘI ĐỒNG ĐÁNH GIÁ NGHIỆM THU (HĐ 03 - 7 THÀNH VIÊN BẮT BUỘC)</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>{{CHU_TICH_HD_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chủ tịch HĐ Đề cương (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Công Khẩn</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>GS.TS.</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
+        </is>
+      </c>
+      <c r="F57">
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C57), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>D02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chủ tịch HĐ Nghiệm thu (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Phạm Văn Hoàn</t>
+          <t>Nguyễn Xuân Ninh</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -1791,55 +1738,55 @@
         </is>
       </c>
       <c r="F58">
-        <f>IF(ISBLANK(C58), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C58), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>D03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Công Khẩn</t>
+          <t>Trần Quang Trung</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>GS.TS.</t>
+          <t>PGS.TS.</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
+          <t>Hiệp hội Sữa Việt Nam</t>
         </is>
       </c>
       <c r="F59">
-        <f>IF(ISBLANK(C59), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C59), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>D04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Đề cương 1 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Lâm</t>
+          <t>Lê Bạch Mai</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -1853,81 +1800,66 @@
         </is>
       </c>
       <c r="F60">
-        <f>IF(ISBLANK(C60), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C60), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>D05</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 1 (Bắt buộc)</t>
+          <t>Ủy viên HĐ Đề cương 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Ninh Thị Nhung</t>
+          <t>Nguyễn Thị Lâm</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.</t>
+          <t>PGS.TS.BS.</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Trường Đại học Y Dược Thái Bình</t>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
         </is>
       </c>
       <c r="F61">
-        <f>IF(ISBLANK(C61), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C61), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 2 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Trần Văn Ơn</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>PGS.TS.</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>Trường Đại học Dược Hà Nội</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F62">
-        <f>IF(ISBLANK(C62), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C62), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đề cương 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F63">
@@ -1938,12 +1870,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>D08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 3 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Đề cương 4 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F64">
@@ -1954,38 +1886,53 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ủy viên HĐ Nghiệm thu 4 (Tùy chọn)</t>
+          <t>Thư ký HĐ Đề cương 1 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Hoàng Hà Linh</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Trung tâm NCKH - Viện VIAM</t>
         </is>
       </c>
       <c r="F65">
-        <f>IF(ISBLANK(C65), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C65), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Thư ký HĐ Nghiệm thu 1 (Bắt buộc)</t>
+          <t>Thư ký HĐ Đề cương 2 (Bắt buộc)</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Hoàng Hà Linh</t>
+          <t>Trương Phan Hồng Hà</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>PGS.TS.BS.</t>
+          <t>Thạc sĩ</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -1994,647 +1941,660 @@
         </is>
       </c>
       <c r="F66">
-        <f>IF(ISBLANK(C66), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C66), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>E10</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Thư ký HĐ Nghiệm thu 2 (Bắt buộc)</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Trương Phan Hồng Hà</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Thạc sĩ</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>Viện Y học Ứng dụng Việt Nam</t>
-        </is>
-      </c>
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>{{SO_QD_TLHD_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Khoa học - Mẫu 05 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="n"/>
       <c r="F67">
-        <f>IF(ISBLANK(C67), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISBLANK(C67), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>SEC_F</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>PHẦN F: LÝ LỊCH KHOA HỌC CHUYÊN GIA (CV CHỦ NHIỆM BẮT BUỘC &amp; CV THÀNH VIÊN TÙY CHỌN)</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="n"/>
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_TLHD_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Khoa học (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="n"/>
+      <c r="F68">
+        <f>IF(ISBLANK(C68), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>F01</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Hồ sơ Chủ nhiệm đề tài (Bắt buộc - File mặc định cho HĐ Đạo đức)</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>Trương Hồng Sơn</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Chủ nhiệm đề tài</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>Lý lịch khoa học - Trương Hồng Sơn.docx</t>
-        </is>
-      </c>
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>{{SO_QD_PHE_DUYET}}</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Số QĐ Phê duyệt đề tài - Mẫu 08 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="n"/>
       <c r="F69">
-        <f>IF(ISBLANK(C69), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", "✅ Đã khai chủ nhiệm đề tài - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C69), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>F02</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Hồ sơ Đồng Chủ nhiệm (Tùy chọn)</t>
-        </is>
-      </c>
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_PHE_DUYET}}</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ Phê duyệt đề tài (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="n"/>
       <c r="F70">
-        <f>IF(ISBLANK(C70), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C70), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>F03</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Hồ sơ Thư ký Đề tài (Tùy chọn)</t>
-        </is>
-      </c>
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>{{NGAY_HOP_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Khoa học - Mẫu 06, 07 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="n"/>
       <c r="F71">
-        <f>IF(ISBLANK(C71), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C71), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>F04</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 4 (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="F72">
-        <f>IF(ISBLANK(C72), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
-        <v/>
-      </c>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>SEC_E</t>
+        </is>
+      </c>
+      <c r="B72" s="2">
+        <f>"PHẦN E: HỘI ĐỒNG ĐÁNH GIÁ NGHIỆM THU " &amp; IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), "🟢 [BẮT BUỘC - ĐANG ÁP DỤNG]", "⚪ [KHÔNG ÁP DỤNG CHO BỘ NÀY]")</f>
+        <v/>
+      </c>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>F05</t>
+          <t>{{CHU_TICH_HD_NGHIEM_THU}}</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 5 (Tùy chọn)</t>
+          <t>Chủ tịch HĐ Nghiệm thu (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Phạm Văn Hoàn</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
         </is>
       </c>
       <c r="F73">
-        <f>IF(ISBLANK(C73), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C73), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 6 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 1 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Công Khẩn</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>GS.TS.</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Hội đồng Đạo đức Y sinh Quốc gia</t>
         </is>
       </c>
       <c r="F74">
-        <f>IF(ISBLANK(C74), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C74), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>F07</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 7 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Lâm</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Nguyên Phó Viện trưởng Viện Dinh dưỡng QG</t>
         </is>
       </c>
       <c r="F75">
-        <f>IF(ISBLANK(C75), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C75), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>F08</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 8 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Nghiệm thu 1 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Ninh Thị Nhung</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Trường Đại học Y Dược Thái Bình</t>
         </is>
       </c>
       <c r="F76">
-        <f>IF(ISBLANK(C76), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C76), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>F09</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 9 (Tùy chọn)</t>
+          <t>Ủy viên HĐ Nghiệm thu 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Trần Văn Ơn</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>PGS.TS.</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Trường Đại học Dược Hà Nội</t>
         </is>
       </c>
       <c r="F77">
-        <f>IF(ISBLANK(C77), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C77), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>F10</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hồ sơ Chuyên gia / Thành viên 10 (Tùy chọn)</t>
+          <t>Ủy viên Phản biện 3 (Tùy chọn)</t>
         </is>
       </c>
       <c r="F78">
-        <f>IF(ISBLANK(C78), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C78), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>SEC_G</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>PHẦN G: SỐ VĂN BẢN, NGÀY KÝ, BỐI CẢNH &amp; LỊCH HỌP (TÙY CHỌN - ĐỂ TRỐNG SẼ GIỮ NGUYÊN DẤU CHẤM LỬNG)</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="n"/>
-      <c r="E79" s="7" t="n"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Ủy viên HĐ Nghiệm thu 3 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F79">
+        <f>IF(ISBLANK(C79), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>G01</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>Bối cảnh / lý do triển khai đề tài (Điền nội dung hoặc để trống)</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>Token: {{BOI_CANH_DU_AN}}</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="n"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ủy viên HĐ Nghiệm thu 4 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F80">
+        <f>IF(ISBLANK(C80), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>G02</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Địa điểm họp Hội đồng (Tùy chọn - Để trống dùng địa chỉ Viện)</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>Token: {{DIA_DIEM_HOP}}</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="n"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Nghiệm thu 1 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Hoàng Hà Linh</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>PGS.TS.BS.</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+      <c r="F81">
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C81), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>G03</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Thời gian họp chung (giờ, ngày tháng - Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>Token: {{THOI_GIAN_HOP}}</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="n"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Thư ký HĐ Nghiệm thu 2 (Bắt buộc)</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Trương Phan Hồng Hà</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Thạc sĩ</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Viện Y học Ứng dụng Việt Nam</t>
+        </is>
+      </c>
+      <c r="F82">
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C82), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>G04</t>
+          <t>{{SO_QD_TLHD_NGHIEM_THU}}</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Số công văn mời chuyên gia (Tùy chọn)</t>
+          <t>Số QĐ TLHĐ Nghiệm thu - Mẫu 9 (Tùy chọn)</t>
         </is>
       </c>
       <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>Token: {{SO_CONG_VAN}}</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="n"/>
+      <c r="F83">
+        <f>IF(ISBLANK(C83), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>G05</t>
+          <t>{{NGAY_QD_TLHD_NGHIEM_THU}}</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Ngày ký công văn mời chuyên gia (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="n"/>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>Định dạng: DD/MM/YYYY</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="n"/>
+          <t>Ngày ký QĐ TLHĐ Nghiệm thu (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="n"/>
+      <c r="F84">
+        <f>IF(ISBLANK(C84), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
         <is>
-          <t>G06</t>
+          <t>{{SO_QD_CONG_NHAN}}</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Số Quyết định giao đề tài - Mẫu 00 (Tùy chọn)</t>
+          <t>Số QĐ Công nhận kết quả - Mẫu 12 (Tùy chọn)</t>
         </is>
       </c>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>Token: {{SO_QD_GIAO_DE_TAI}}</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="n"/>
+      <c r="F85">
+        <f>IF(ISBLANK(C85), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>G07</t>
+          <t>{{NGAY_QD_CONG_NHAN}}</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Ngày ký QĐ giao đề tài (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="n"/>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>Định dạng: DD/MM/YYYY</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="n"/>
+          <t>Ngày ký QĐ Công nhận kết quả (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="n"/>
+      <c r="F86">
+        <f>IF(ISBLANK(C86), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
-          <t>G08</t>
+          <t>{{NGAY_HOP_NGHIEM_THU}}</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Số QĐ TLHĐ Đạo đức - Mẫu 01 (Tùy chọn)</t>
+          <t>Ngày họp HĐ Nghiệm thu - Mẫu 10, 11 (Tùy chọn)</t>
         </is>
       </c>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>Token: {{SO_QD_TLHD_DAO_DUC}}</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="n"/>
+      <c r="F87">
+        <f>IF(ISBLANK(C87), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>G09</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>Ngày ký QĐ TLHĐ Đạo đức (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="n"/>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>Định dạng: DD/MM/YYYY</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="n"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>SEC_F</t>
+        </is>
+      </c>
+      <c r="B88" s="2">
+        <f>"PHẦN F: LÝ LỊCH KHOA HỌC CHUYÊN GIA (CV) " &amp; IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), "🟢 [BẮT BUỘC CV CHỦ NHIỆM]", "⚪ [TÙY CHỌN]")</f>
+        <v/>
+      </c>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>G10</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Số QĐ TLHĐ Khoa học - Mẫu 05 (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>Token: {{SO_QD_TLHD_KHOA_HOC}}</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="n"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>F01</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Hồ sơ Chủ nhiệm đề tài (Bắt buộc - File mặc định cho HĐ Đạo đức)</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Trương Hồng Sơn</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Chủ nhiệm đề tài</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>Lý lịch khoa học - Trương Hồng Sơn.docx</t>
+        </is>
+      </c>
+      <c r="F89">
+        <f>IF(ISBLANK(C89), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>Ngày ký QĐ TLHĐ Khoa học (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="n"/>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>Định dạng: DD/MM/YYYY</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="n"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>F02</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Hồ sơ Đồng Chủ nhiệm (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F90">
+        <f>IF(ISBLANK(C90), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t>G12</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
-        <is>
-          <t>Số QĐ TLHĐ Nghiệm thu - Mẫu 9 (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t>Token: {{SO_QD_TLHD_NGHIEM_THU}}</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="n"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>F03</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Hồ sơ Thư ký Đề tài (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F91">
+        <f>IF(ISBLANK(C91), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>G13</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Ngày ký QĐ TLHĐ Nghiệm thu (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="n"/>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>Định dạng: DD/MM/YYYY</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="n"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>F04</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Hồ sơ Chuyên gia / Thành viên 4 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F92">
+        <f>IF(ISBLANK(C92), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>G14</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Số QĐ Phê duyệt đề tài - Mẫu 08 (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t>Token: {{SO_QD_PHE_DUYET}}</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="n"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>F05</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Hồ sơ Chuyên gia / Thành viên 5 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F93">
+        <f>IF(ISBLANK(C93), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>G15</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>Ngày ký QĐ Phê duyệt đề tài (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="n"/>
-      <c r="D94" s="8" t="inlineStr">
-        <is>
-          <t>Định dạng: DD/MM/YYYY</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="n"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>F06</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Hồ sơ Chuyên gia / Thành viên 6 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F94">
+        <f>IF(ISBLANK(C94), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>G16</t>
-        </is>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>Số QĐ Công nhận kết quả - Mẫu 12 (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="n"/>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t>Token: {{SO_QD_CONG_NHAN}}</t>
-        </is>
-      </c>
-      <c r="E95" s="8" t="n"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>F07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Hồ sơ Chuyên gia / Thành viên 7 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F95">
+        <f>IF(ISBLANK(C95), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>G17</t>
-        </is>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>Ngày ký QĐ Công nhận kết quả (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="n"/>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>Định dạng: DD/MM/YYYY</t>
-        </is>
-      </c>
-      <c r="E96" s="8" t="n"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>F08</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Hồ sơ Chuyên gia / Thành viên 8 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F96">
+        <f>IF(ISBLANK(C96), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>G18</t>
-        </is>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
-        <is>
-          <t>Ngày họp HĐ Đạo đức - Mẫu 02, 03 (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="n"/>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>Định dạng: DD/MM/YYYY</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>G19</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>Ngày họp HĐ Khoa học - Mẫu 06, 07 (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="n"/>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>Định dạng: DD/MM/YYYY</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>G20</t>
-        </is>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>Ngày họp HĐ Nghiệm thu - Mẫu 10, 11 (Tùy chọn)</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="n"/>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>Định dạng: DD/MM/YYYY</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="n"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Hồ sơ Chuyên gia / Thành viên 9 (Tùy chọn)</t>
+        </is>
+      </c>
+      <c r="F97">
+        <f>IF(ISBLANK(C97), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation sqref="C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='_NhanSu'!$A$2:$A$16</formula1>
-    </dataValidation>
+  <dataValidations count="7">
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Nghiên cứu can thiệp,Nghiên cứu quan sát,Thử nghiệm lâm sàng,Đánh giá hiệu quả công thức,Khác"</formula1>
     </dataValidation>
-    <dataValidation sqref="D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"GS.TS.,PGS.TS.,TS.,ThS.,BS.CKII,BS.CKI,BS.,CN.,DS."</formula1>
-    </dataValidation>
-    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24 A25 A26 A27 A28 A29 A30 A31 A32 A33 A34 A36 A37 A38 A39 A40 A41 A42 A43 A44 A45 A47 A48 A49 A50 A51 A52 A53 A54 A55 A56 A58 A59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='_Tokens'!$A$2:$A$38</formula1>
-    </dataValidation>
     <dataValidation sqref="C84 C86 C88 C90 C92 C94 C96 C97 C98 C99" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Sai định dạng ngày" error="Vui lòng nhập ngày hợp lệ (VD: 15/03/2027 hoặc chọn từ lịch)" promptTitle="Nhập ngày" prompt="Định dạng ngày: DD/MM/YYYY" type="date" operator="greaterThanOrEqual">
       <formula1>DATE(1900,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"full,dao_duc,khoa_hoc,nghiem_thu"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C44 C45 C46 C47 C48 C49 C50 C51 C52 C58 C59 C60 C61 C62 C63 C64 C65 C66 C74 C75 C76 C77 C78 C79 C80 C81 C82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='_NhanSu'!$A$2:$A$16</formula1>
+    </dataValidation>
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20 A22 A23 A24 A25 A26 A27 A28 A29 A30 A31 A32 A33 A34 A35 A36 A37 A38 A39 A40 A41 A43 A44 A45 A46 A47 A48 A49 A50 A51 A52 A53 A54 A55 A57 A58 A59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='_Tokens'!$A$2:$A$49</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='_BoHoSo'!$A$2:$A$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39 D40 D41 D44 D45 D46 D47 D48 D49 D50 D51 D52 D58 D59 D60 D61 D62 D63 D64 D65 D66 D74 D75 D76 D77 D78 D79 D80 D81 D82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"GS.TS.,PGS.TS.,TS.,ThS.,BS.CKII,BS.CKI,BS.,CN.,DS."</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2667,11 +2627,27 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="5">
-        <f>IF(COUNTIF(F6:F150, "*BÁO LỖI*")&gt;0, "⚠️ BÁO LỖI: PHÁT HIỆN CHƯA CÓ FILE CV CHUYÊN GIA HOẶC THIẾU THÔNG TIN BẮT BUỘC - VUI LÒNG BỔ SUNG CÁC Ô MÀU ĐỎ DƯỚI ĐÂY", "🎉 HOÀN THÀNH 100%: TẤT CẢ THÔNG TIN &amp; FILE CV CHUYÊN GIA ĐÃ ĐẦY ĐỦ - SẴN SÀNG CHẠY RA BỘ HỒ SƠ HOÀN CHỈNH")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3"/>
+        <f>IF(COUNTIF(F6:F150, "*BÁO LỖI*")&gt;0, "⚠️ BÁO LỖI: PHÁT HIỆN THIẾU THÔNG TIN BẮT BUỘC CỦA BỘ HỒ SƠ ĐÃ CHỌN - VUI LÒNG BỔ SUNG CÁC Ô MÀU ĐỎ DƯỚI ĐÂY", "🎉 HOÀN THÀNH 100%: TẤT CẢ THÔNG TIN BẮT BUỘC CHO BỘ HỒ SƠ ĐÃ CHỌN ĐÃ ĐẦY ĐỦ - SẴN SÀNG CHẠY RA BỘ HỒ SƠ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BO_HO_SO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CHỌN BỘ HỒ SƠ (A: NCKH &amp; Đánh giá công thức / B: Thử nghiệm lâm sàng / C: Quan sát dịch tễ / D: Chuyển giao CN)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -2712,7 +2688,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PHẦN A: THÔNG TIN CHUNG DỰ ÁN &amp; ĐỀ TÀI</t>
+          <t>PHẦN A: THÔNG TIN CHUNG DỰ ÁN &amp; ĐỀ TÀI (BẮT BUỘC TẤT CẢ CÁC BỘ)</t>
         </is>
       </c>
       <c r="C5" s="2" t="n"/>
@@ -2723,7 +2699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>{{TEN_DE_TAI}}</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2742,7 +2718,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A02</t>
+          <t>{{LOAI_HINH_NC}}</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2761,7 +2737,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>{{NAM}}</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2780,7 +2756,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A04</t>
+          <t>{{DON_VI_CHU_TRI}}</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2799,7 +2775,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>{{THOI_GIAN_BAT_DAU}}</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2818,7 +2794,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>{{DON_VI_DOI_TAC}}</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2837,7 +2813,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>{{DIA_DIEM_TRIEN_KHAI}}</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2856,7 +2832,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>{{DAU_MOI_LIEN_HE}}</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2880,7 +2856,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PHẦN B: BAN CHỦ NHIỆM &amp; NGHIÊN CỨU VIÊN ĐỀ TÀI (TỐI ĐA 20 NGƯỜI)</t>
+          <t>PHẦN B: BAN CHỦ NHIỆM &amp; NGHIÊN CỨU VIÊN ĐỀ TÀI (CHỦ NHIỆM BẮT BUỘC)</t>
         </is>
       </c>
       <c r="C14" s="2" t="n"/>
@@ -2891,7 +2867,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B01</t>
+          <t>{{CHU_NHIEM_HO_TEN}}</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2910,7 +2886,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B02</t>
+          <t>{{DONG_CHU_NHIEM_HO_TEN}}</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2926,7 +2902,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B03</t>
+          <t>{{THU_KY_DE_TAI}}</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2942,7 +2918,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B04</t>
+          <t>{{DANH_SACH_NGHIEN_CUU_VIEN}}</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3217,10 +3193,9 @@
           <t>SEC_C</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>PHẦN C: HỘI ĐỒNG ĐẠO ĐỨC TRONG NGHIÊN CỨU (HĐ 01 - 7 THÀNH VIÊN BẮT BUỘC)</t>
-        </is>
+      <c r="B35" s="2">
+        <f>"PHẦN C: HỘI ĐỒNG ĐẠO ĐỨC TRONG NGHIÊN CỨU " &amp; IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), "🟢 [BẮT BUỘC - ĐANG ÁP DỤNG]", "⚪ [KHÔNG ÁP DỤNG CHO BỘ NÀY]")</f>
+        <v/>
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n"/>
@@ -3230,7 +3205,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>{{CHU_TICH_HD_DAO_DUC}}</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3242,7 +3217,7 @@
       <c r="D36" s="3" t="inlineStr"/>
       <c r="E36" s="3" t="inlineStr"/>
       <c r="F36">
-        <f>IF(ISBLANK(C36), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C36), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3261,7 +3236,7 @@
       <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37">
-        <f>IF(ISBLANK(C37), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C37), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3280,7 +3255,7 @@
       <c r="D38" s="3" t="inlineStr"/>
       <c r="E38" s="3" t="inlineStr"/>
       <c r="F38">
-        <f>IF(ISBLANK(C38), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C38), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3299,7 +3274,7 @@
       <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="3" t="inlineStr"/>
       <c r="F39">
-        <f>IF(ISBLANK(C39), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C39), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3318,7 +3293,7 @@
       <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="3" t="inlineStr"/>
       <c r="F40">
-        <f>IF(ISBLANK(C40), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C40), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3385,7 +3360,7 @@
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
       <c r="F44">
-        <f>IF(ISBLANK(C44), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C44), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3404,7 +3379,7 @@
       <c r="D45" s="3" t="inlineStr"/>
       <c r="E45" s="3" t="inlineStr"/>
       <c r="F45">
-        <f>IF(ISBLANK(C45), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C45), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3414,10 +3389,9 @@
           <t>SEC_D</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>PHẦN D: HỘI ĐỒNG KHOA HỌC XÉT DUYỆT ĐỀ CƯƠNG (HĐ 02 - 7 THÀNH VIÊN BẮT BUỘC)</t>
-        </is>
+      <c r="B46" s="2">
+        <f>"PHẦN D: HỘI ĐỒNG KHOA HỌC XÉT DUYỆT ĐỀ CƯƠNG " &amp; IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), "🟢 [BẮT BUỘC - ĐANG ÁP DỤNG]", "⚪ [KHÔNG ÁP DỤNG CHO BỘ NÀY]")</f>
+        <v/>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n"/>
@@ -3427,7 +3401,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>{{CHU_TICH_HD_KHOA_HOC}}</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3439,7 +3413,7 @@
       <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47">
-        <f>IF(ISBLANK(C47), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C47), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3458,7 +3432,7 @@
       <c r="D48" s="3" t="inlineStr"/>
       <c r="E48" s="3" t="inlineStr"/>
       <c r="F48">
-        <f>IF(ISBLANK(C48), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C48), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3477,7 +3451,7 @@
       <c r="D49" s="3" t="inlineStr"/>
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49">
-        <f>IF(ISBLANK(C49), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C49), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3496,7 +3470,7 @@
       <c r="D50" s="3" t="inlineStr"/>
       <c r="E50" s="3" t="inlineStr"/>
       <c r="F50">
-        <f>IF(ISBLANK(C50), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C50), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3515,7 +3489,7 @@
       <c r="D51" s="3" t="inlineStr"/>
       <c r="E51" s="3" t="inlineStr"/>
       <c r="F51">
-        <f>IF(ISBLANK(C51), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C51), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3582,7 +3556,7 @@
       <c r="D55" s="3" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr"/>
       <c r="F55">
-        <f>IF(ISBLANK(C55), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C55), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3601,7 +3575,7 @@
       <c r="D56" s="3" t="inlineStr"/>
       <c r="E56" s="3" t="inlineStr"/>
       <c r="F56">
-        <f>IF(ISBLANK(C56), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("khoa_hoc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C56), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3611,10 +3585,9 @@
           <t>SEC_E</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>PHẦN E: HỘI ĐỒNG ĐÁNH GIÁ NGHIỆM THU (HĐ 03 - 7 THÀNH VIÊN BẮT BUỘC)</t>
-        </is>
+      <c r="B57" s="2">
+        <f>"PHẦN E: HỘI ĐỒNG ĐÁNH GIÁ NGHIỆM THU " &amp; IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), "🟢 [BẮT BUỘC - ĐANG ÁP DỤNG]", "⚪ [KHÔNG ÁP DỤNG CHO BỘ NÀY]")</f>
+        <v/>
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n"/>
@@ -3624,7 +3597,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>{{CHU_TICH_HD_NGHIEM_THU}}</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3636,7 +3609,7 @@
       <c r="D58" s="3" t="inlineStr"/>
       <c r="E58" s="3" t="inlineStr"/>
       <c r="F58">
-        <f>IF(ISBLANK(C58), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C58), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3655,7 +3628,7 @@
       <c r="D59" s="3" t="inlineStr"/>
       <c r="E59" s="3" t="inlineStr"/>
       <c r="F59">
-        <f>IF(ISBLANK(C59), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C59), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3674,7 +3647,7 @@
       <c r="D60" s="3" t="inlineStr"/>
       <c r="E60" s="3" t="inlineStr"/>
       <c r="F60">
-        <f>IF(ISBLANK(C60), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C60), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3693,7 +3666,7 @@
       <c r="D61" s="3" t="inlineStr"/>
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61">
-        <f>IF(ISBLANK(C61), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C61), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3712,7 +3685,7 @@
       <c r="D62" s="3" t="inlineStr"/>
       <c r="E62" s="3" t="inlineStr"/>
       <c r="F62">
-        <f>IF(ISBLANK(C62), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C62), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3779,7 +3752,7 @@
       <c r="D66" s="3" t="inlineStr"/>
       <c r="E66" s="3" t="inlineStr"/>
       <c r="F66">
-        <f>IF(ISBLANK(C66), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C66), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3798,7 +3771,7 @@
       <c r="D67" s="3" t="inlineStr"/>
       <c r="E67" s="3" t="inlineStr"/>
       <c r="F67">
-        <f>IF(ISBLANK(C67), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
+        <f>IF(ISNUMBER(SEARCH("nghiem_thu", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), IF(ISBLANK(C67), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong"), "⚪ Không yêu cầu cho bộ này")</f>
         <v/>
       </c>
     </row>
@@ -3808,10 +3781,9 @@
           <t>SEC_F</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>PHẦN F: LÝ LỊCH KHOA HỌC CHUYÊN GIA (CV CHỦ NHIỆM BẮT BUỘC &amp; CV THÀNH VIÊN TÙY CHỌN)</t>
-        </is>
+      <c r="B68" s="2">
+        <f>"PHẦN F: LÝ LỊCH KHOA HỌC CHUYÊN GIA (CV) " &amp; IF(ISNUMBER(SEARCH("dao_duc", VLOOKUP($C$3, _BoHoSo!$A$2:$D$8, 4, FALSE))), "🟢 [BẮT BUỘC CV CHỦ NHIỆM]", "⚪ [TÙY CHỌN]")</f>
+        <v/>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n"/>
@@ -3833,7 +3805,7 @@
       <c r="D69" s="3" t="n"/>
       <c r="E69" s="3" t="n"/>
       <c r="F69">
-        <f>IF(ISBLANK(C69), "❌ CHƯA ĐIỀN THÔNG TIN CNĐT (BÁO LỖI)", "✅ Đã khai chủ nhiệm đề tài - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C69), "❌ CHƯA ĐIỀN (BÁO LỖI)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
@@ -3849,7 +3821,7 @@
         </is>
       </c>
       <c r="F70">
-        <f>IF(ISBLANK(C70), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C70), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
@@ -3865,7 +3837,7 @@
         </is>
       </c>
       <c r="F71">
-        <f>IF(ISBLANK(C71), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C71), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
@@ -3881,7 +3853,7 @@
         </is>
       </c>
       <c r="F72">
-        <f>IF(ISBLANK(C72), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C72), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
@@ -3897,7 +3869,7 @@
         </is>
       </c>
       <c r="F73">
-        <f>IF(ISBLANK(C73), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C73), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
@@ -3913,7 +3885,7 @@
         </is>
       </c>
       <c r="F74">
-        <f>IF(ISBLANK(C74), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C74), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
@@ -3929,7 +3901,7 @@
         </is>
       </c>
       <c r="F75">
-        <f>IF(ISBLANK(C75), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C75), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
@@ -3945,7 +3917,7 @@
         </is>
       </c>
       <c r="F76">
-        <f>IF(ISBLANK(C76), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C76), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
@@ -3961,7 +3933,7 @@
         </is>
       </c>
       <c r="F77">
-        <f>IF(ISBLANK(C77), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C77), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
@@ -3977,7 +3949,7 @@
         </is>
       </c>
       <c r="F78">
-        <f>IF(ISBLANK(C78), "⚪ Tùy chọn (Trống)", "✅ Đã khai tên - CV sẽ tự khớp theo tên")</f>
+        <f>IF(ISBLANK(C78), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
         <v/>
       </c>
     </row>
@@ -4014,6 +3986,10 @@
         </is>
       </c>
       <c r="E80" s="8" t="n"/>
+      <c r="F80">
+        <f>IF(ISBLANK(C80), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -4033,6 +4009,10 @@
         </is>
       </c>
       <c r="E81" s="8" t="n"/>
+      <c r="F81">
+        <f>IF(ISBLANK(C81), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
@@ -4052,6 +4032,10 @@
         </is>
       </c>
       <c r="E82" s="8" t="n"/>
+      <c r="F82">
+        <f>IF(ISBLANK(C82), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
@@ -4071,6 +4055,10 @@
         </is>
       </c>
       <c r="E83" s="8" t="n"/>
+      <c r="F83">
+        <f>IF(ISBLANK(C83), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
@@ -4090,6 +4078,10 @@
         </is>
       </c>
       <c r="E84" s="8" t="n"/>
+      <c r="F84">
+        <f>IF(ISBLANK(C84), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -4109,6 +4101,10 @@
         </is>
       </c>
       <c r="E85" s="8" t="n"/>
+      <c r="F85">
+        <f>IF(ISBLANK(C85), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
@@ -4128,6 +4124,10 @@
         </is>
       </c>
       <c r="E86" s="8" t="n"/>
+      <c r="F86">
+        <f>IF(ISBLANK(C86), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
@@ -4147,6 +4147,10 @@
         </is>
       </c>
       <c r="E87" s="8" t="n"/>
+      <c r="F87">
+        <f>IF(ISBLANK(C87), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
@@ -4166,6 +4170,10 @@
         </is>
       </c>
       <c r="E88" s="8" t="n"/>
+      <c r="F88">
+        <f>IF(ISBLANK(C88), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -4185,6 +4193,10 @@
         </is>
       </c>
       <c r="E89" s="8" t="n"/>
+      <c r="F89">
+        <f>IF(ISBLANK(C89), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
@@ -4204,6 +4216,10 @@
         </is>
       </c>
       <c r="E90" s="8" t="n"/>
+      <c r="F90">
+        <f>IF(ISBLANK(C90), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -4223,6 +4239,10 @@
         </is>
       </c>
       <c r="E91" s="8" t="n"/>
+      <c r="F91">
+        <f>IF(ISBLANK(C91), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
@@ -4242,6 +4262,10 @@
         </is>
       </c>
       <c r="E92" s="8" t="n"/>
+      <c r="F92">
+        <f>IF(ISBLANK(C92), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -4261,6 +4285,10 @@
         </is>
       </c>
       <c r="E93" s="8" t="n"/>
+      <c r="F93">
+        <f>IF(ISBLANK(C93), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
@@ -4280,6 +4308,10 @@
         </is>
       </c>
       <c r="E94" s="8" t="n"/>
+      <c r="F94">
+        <f>IF(ISBLANK(C94), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -4299,6 +4331,10 @@
         </is>
       </c>
       <c r="E95" s="8" t="n"/>
+      <c r="F95">
+        <f>IF(ISBLANK(C95), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -4318,6 +4354,10 @@
         </is>
       </c>
       <c r="E96" s="8" t="n"/>
+      <c r="F96">
+        <f>IF(ISBLANK(C96), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="8" t="inlineStr">
@@ -4337,6 +4377,10 @@
         </is>
       </c>
       <c r="E97" s="8" t="n"/>
+      <c r="F97">
+        <f>IF(ISBLANK(C97), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
@@ -4356,6 +4400,10 @@
         </is>
       </c>
       <c r="E98" s="8" t="n"/>
+      <c r="F98">
+        <f>IF(ISBLANK(C98), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -4375,27 +4423,34 @@
         </is>
       </c>
       <c r="E99" s="8" t="n"/>
+      <c r="F99">
+        <f>IF(ISBLANK(C99), "⚪ Tùy chọn (Trống)", "✅ Xong")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation sqref="C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='_NhanSu'!$A$2:$A$16</formula1>
-    </dataValidation>
+  <dataValidations count="6">
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Nghiên cứu can thiệp,Nghiên cứu quan sát,Thử nghiệm lâm sàng,Đánh giá hiệu quả công thức,Khác"</formula1>
     </dataValidation>
-    <dataValidation sqref="D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"GS.TS.,PGS.TS.,TS.,ThS.,BS.CKII,BS.CKI,BS.,CN.,DS."</formula1>
+    <dataValidation sqref="C84 C86 C88 C90 C92 C94 C96 C97 C98 C99" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Sai định dạng ngày" error="Vui lòng nhập ngày hợp lệ (VD: 15/03/2027 hoặc chọn từ lịch)" promptTitle="Nhập ngày" prompt="Định dạng ngày: DD/MM/YYYY" type="date" operator="greaterThanOrEqual">
+      <formula1>DATE(1900,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C37 C38 C39 C40 C41 C42 C43 C44 C45 C48 C49 C50 C51 C52 C53 C54 C55 C56 C59 C60 C61 C62 C63 C64 C65 C66 C67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='_NhanSu'!$A$2:$A$16</formula1>
     </dataValidation>
     <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24 A25 A26 A27 A28 A29 A30 A31 A32 A33 A34 A36 A37 A38 A39 A40 A41 A42 A43 A44 A45 A47 A48 A49 A50 A51 A52 A53 A54 A55 A56 A58 A59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='_Tokens'!$A$2:$A$38</formula1>
+      <formula1>='_Tokens'!$A$2:$A$49</formula1>
     </dataValidation>
-    <dataValidation sqref="C84 C86 C88 C90 C92 C94 C96 C97 C98 C99" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Sai định dạng ngày" error="Vui lòng nhập ngày hợp lệ (VD: 15/03/2027 hoặc chọn từ lịch)" promptTitle="Nhập ngày" prompt="Định dạng ngày: DD/MM/YYYY" type="date" operator="greaterThanOrEqual">
-      <formula1>DATE(1900,1,1)</formula1>
+    <dataValidation sqref="C3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='_BoHoSo'!$A$2:$A$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D37 D38 D39 D40 D41 D42 D43 D44 D45 D48 D49 D50 D51 D52 D53 D54 D55 D56 D59 D60 D61 D62 D63 D64 D65 D66 D67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"GS.TS.,PGS.TS.,TS.,ThS.,BS.CKII,BS.CKI,BS.,CN.,DS."</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4719,6 +4774,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24 A25 A26 A27 A28 A29 A30 A31 A32 A33 A34 A35 A36 A37 A38 A39 A40 A41 A42 A43 A44 A45 A46 A47 A48 A49 A50 A51 A52 A53 A54 A55 A56 A57 A58 A59 A60 A61 A62 A63 A64 A65 A66 A67 A68 A69 A70 A71 A72 A73 A74 A75 A76 A77 A78 A79 A80 A81 A82 A83 A84 A85 A86 A87 A88 A89 A90 A91 A92 A93 A94 A95 A96 A97 A98 A99 A100 A101 A102 A103 A104 A105 A106 A107 A108 A109 A110 A111 A112 A113 A114 A115 A116 A117 A118 A119 A120 A121 A122 A123 A124 A125 A126 A127 A128 A129 A130 A131 A132 A133 A134 A135 A136 A137 A138 A139 A140 A141 A142 A143 A144 A145 A146 A147 A148 A149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>_Tokens!$A$2:$A$100</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4729,7 +4789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4983,398 +5043,815 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Danh sách nghiên cứu viên</t>
+          <t>Danh sách nghiên cứu viên (có đánh số)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>{{CHU_TICH_HD_DAO_DUC}}</t>
+          <t>{{NGHIEN_CUU_VIEN_1}}</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chủ tịch HĐ Đạo đức</t>
+          <t>Nghiên cứu viên 1 - Họ tên có học vị</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>{{CHU_TICH_HD_KHOA_HOC}}</t>
+          <t>{{NGHIEN_CUU_VIEN_1_TEN}}</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D01</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chủ tịch HĐ Khoa học</t>
+          <t>Nghiên cứu viên 1 - Chỉ họ tên</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>{{CHU_TICH_HD_NGHIEM_THU}}</t>
+          <t>{{NGHIEN_CUU_VIEN_1_DON_VI}}</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>B04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chủ tịch HĐ Nghiệm thu</t>
+          <t>Nghiên cứu viên 1 - Đơn vị công tác</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{{BOI_CANH_DU_AN}}</t>
+          <t>{{NGHIEN_CUU_VIEN_2}}</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>G01</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bối cảnh / lý do triển khai đề tài</t>
+          <t>Nghiên cứu viên 2 - Họ tên có học vị</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{{DIA_DIEM_HOP}}</t>
+          <t>{{NGHIEN_CUU_VIEN_2_TEN}}</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>G02</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Địa điểm họp Hội đồng</t>
+          <t>Nghiên cứu viên 2 - Chỉ họ tên</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{{THOI_GIAN_HOP}}</t>
+          <t>{{NGHIEN_CUU_VIEN_2_DON_VI}}</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>G03</t>
+          <t>B05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thời gian họp Hội đồng (giờ, ngày tháng)</t>
+          <t>Nghiên cứu viên 2 - Đơn vị công tác</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{{SO_CONG_VAN}}</t>
+          <t>{{NGHIEN_CUU_VIEN_3}}</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>G04</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Số công văn mời chuyên gia</t>
+          <t>Nghiên cứu viên 3 - Họ tên có học vị</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{{NGAY_CONG_VAN}}</t>
+          <t>{{NGHIEN_CUU_VIEN_3_TEN}}</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>G05</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ngày ký công văn mời chuyên gia</t>
+          <t>Nghiên cứu viên 3 - Chỉ họ tên</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{{SO_QD_GIAO_DE_TAI}}</t>
+          <t>{{NGHIEN_CUU_VIEN_3_DON_VI}}</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>G06</t>
+          <t>B06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Số Quyết định giao đề tài (00)</t>
+          <t>Nghiên cứu viên 3 - Đơn vị công tác</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{{NGAY_QD_GIAO_DE_TAI}}</t>
+          <t>{{NGHIEN_CUU_VIEN_4}}</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>G07</t>
+          <t>B07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ngày ký QĐ giao đề tài</t>
+          <t>Nghiên cứu viên 4 - Họ tên có học vị</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>{{SO_QD_TLHD_DAO_DUC}}</t>
+          <t>{{NGHIEN_CUU_VIEN_5}}</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>G08</t>
+          <t>B08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Số QĐ TLHĐ Đạo đức (01)</t>
+          <t>Nghiên cứu viên 5 - Họ tên có học vị</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>{{NGAY_QD_TLHD_DAO_DUC}}</t>
+          <t>{{CHU_TICH_HD_DAO_DUC}}</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>G09</t>
+          <t>C01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ngày ký QĐ TLHĐ Đạo đức</t>
+          <t>Chủ tịch HĐ Đạo đức</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>{{SO_QD_TLHD_KHOA_HOC}}</t>
+          <t>{{CHU_TICH_HD_KHOA_HOC}}</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>G10</t>
+          <t>D01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Số QĐ TLHĐ Khoa học (05)</t>
+          <t>Chủ tịch HĐ Khoa học</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>{{NGAY_QD_TLHD_KHOA_HOC}}</t>
+          <t>{{CHU_TICH_HD_NGHIEM_THU}}</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>G11</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ngày ký QĐ TLHĐ Khoa học</t>
+          <t>Chủ tịch HĐ Nghiệm thu</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>{{SO_QD_TLHD_PHE_DUYET}}</t>
+          <t>{{BOI_CANH_DU_AN}}</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>G14</t>
+          <t>G01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Số QĐ Phê duyệt đề tài (08)</t>
+          <t>Bối cảnh / lý do triển khai đề tài</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>{{NGAY_QD_PHE_DUYET}}</t>
+          <t>{{DIA_DIEM_HOP}}</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>G15</t>
+          <t>G02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ngày ký QĐ Phê duyệt đề tài</t>
+          <t>Địa điểm họp Hội đồng</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>{{SO_QD_TLHD_NGHIEM_THU}}</t>
+          <t>{{THOI_GIAN_HOP}}</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>G12</t>
+          <t>G03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Số QĐ TLHĐ Nghiệm thu (9)</t>
+          <t>Thời gian họp Hội đồng (giờ, ngày tháng)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>{{NGAY_QD_TLHD_NGHIEM_THU}}</t>
+          <t>{{SO_CONG_VAN}}</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>G13</t>
+          <t>G04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ngày ký QĐ TLHĐ Nghiệm thu</t>
+          <t>Số công văn mời chuyên gia</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>{{SO_QD_CONG_NHAN}}</t>
+          <t>{{NGAY_CONG_VAN}}</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>G16</t>
+          <t>G05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Số QĐ Công nhận kết quả (12)</t>
+          <t>Ngày ký công văn mời chuyên gia</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>{{NGAY_QD_CONG_NHAN}}</t>
+          <t>{{SO_QD_GIAO_DE_TAI}}</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>G17</t>
+          <t>G06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ngày ký QĐ Công nhận kết quả</t>
+          <t>Số Quyết định giao đề tài (00)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>{{NGAY_HOP_DAO_DUC}}</t>
+          <t>{{NGAY_QD_GIAO_DE_TAI}}</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>G18</t>
+          <t>G07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ngày họp HĐ Đạo đức (02, 03)</t>
+          <t>Ngày ký QĐ giao đề tài</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>{{NGAY_HOP_KHOA_HOC}}</t>
+          <t>{{SO_QD_TLHD_DAO_DUC}}</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>G19</t>
+          <t>G08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ngày họp HĐ Khoa học (06, 07)</t>
+          <t>Số QĐ TLHĐ Đạo đức (01)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>{{NGAY_QD_TLHD_DAO_DUC}}</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>G09</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Đạo đức</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>{{SO_QD_TLHD_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Khoa học (05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_TLHD_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Khoa học</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>{{SO_QD_TLHD_PHE_DUYET}}</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>G14</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Số QĐ Phê duyệt đề tài (08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_PHE_DUYET}}</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>G15</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ Phê duyệt đề tài</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>{{SO_QD_TLHD_NGHIEM_THU}}</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>G12</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Số QĐ TLHĐ Nghiệm thu (9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_TLHD_NGHIEM_THU}}</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>G13</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ TLHĐ Nghiệm thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>{{SO_QD_CONG_NHAN}}</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>G16</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Số QĐ Công nhận kết quả (12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>{{NGAY_QD_CONG_NHAN}}</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>G17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ngày ký QĐ Công nhận kết quả</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>{{NGAY_HOP_DAO_DUC}}</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>G18</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Đạo đức (02, 03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>{{NGAY_HOP_KHOA_HOC}}</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>G19</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ngày họp HĐ Khoa học (06, 07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>{{NGAY_HOP_NGHIEM_THU}}</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>G20</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Ngày họp HĐ Nghiệm thu (10, 11)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MÃ_BỘ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TÊN_BỘ_HỒ_SƠ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MÔ_TẢ_PHẠM_VI</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CÁC_PHẦN_XUẤT</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>THƯ_MỤC_MẪU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bộ A: Hồ sơ NCKH &amp; Đánh giá hiệu quả công thức (Trọn bộ)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bao gồm đầy đủ 3 Hội đồng: Đạo đức, Khoa học và Nghiệm thu (kèm Thư mời chuyên gia &amp; CV)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>dao_duc, khoa_hoc, nghiem_thu</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>01. Hồ sơ đạo đức đề cương - MẪU, 02. Hồ sơ khoa học đề cương - MẪU, 04. Hồ sơ nghiệm thu - MẪU</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A_dao_duc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bộ A (Phần 1): Hồ sơ Đạo đức đề cương</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Gồm hồ sơ Hội đồng Đạo đức (kèm Thư mời chuyên gia đạo đức &amp; CV Chủ nhiệm)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>dao_duc</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>01. Hồ sơ đạo đức đề cương - MẪU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A_khoa_hoc</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bộ A (Phần 2): Hồ sơ Khoa học đề cương</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gồm hồ sơ Hội đồng Khoa học xét duyệt đề cương (kèm Thư mời chuyên gia khoa học)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>khoa_hoc</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>02. Hồ sơ khoa học đề cương - MẪU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A_nghiem_thu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bộ A (Phần 3): Hồ sơ Nghiệm thu đề tài</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gồm hồ sơ Hội đồng Nghiệm thu kết quả (kèm Thư mời chuyên gia nghiệm thu)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>nghiem_thu</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>04. Hồ sơ nghiệm thu - MẪU</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bộ B: Hồ sơ Thử nghiệm lâm sàng (TNLS)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bộ hồ sơ phục vụ đề tài Thử nghiệm lâm sàng / Can thiệp lâm sàng (Setup sẵn cho tương lai)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dao_duc, khoa_hoc, nghiem_thu</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>01. Hồ sơ đạo đức đề cương - MẪU, 02. Hồ sơ khoa học đề cương - MẪU, 04. Hồ sơ nghiệm thu - MẪU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bộ C: Hồ sơ Nghiên cứu quan sát &amp; Khảo sát dịch tễ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bộ hồ sơ phục vụ nghiên cứu quan sát, điều tra dịch tễ cộng đồng (Setup sẵn cho tương lai)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dao_duc, khoa_hoc, nghiem_thu</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>01. Hồ sơ đạo đức đề cương - MẪU, 02. Hồ sơ khoa học đề cương - MẪU, 04. Hồ sơ nghiệm thu - MẪU</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bộ D: Hồ sơ Tư vấn sản phẩm &amp; Chuyển giao công nghệ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bộ hồ sơ phục vụ dự án tư vấn công thức và chuyển giao công nghệ sản phẩm (Setup sẵn cho tương lai)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dao_duc, khoa_hoc, nghiem_thu</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>01. Hồ sơ đạo đức đề cương - MẪU, 02. Hồ sơ khoa học đề cương - MẪU, 04. Hồ sơ nghiệm thu - MẪU</t>
         </is>
       </c>
     </row>
